--- a/05_תוצרים/לוח_זמנים_שלונסקי_53_ישראל_פועלים_סינים.xlsx
+++ b/05_תוצרים/לוח_זמנים_שלונסקי_53_ישראל_פועלים_סינים.xlsx
@@ -154,7 +154,7 @@
     <t>מקדם תפוקה:</t>
   </si>
   <si>
-    <t>משכי הבסיס מחושבים לימי עבודה של 8 שעות. המשך בפועל = משך הבסיס ÷ מקדם התפוקה (מעוגל כלפי מעלה). ב-10 שעות ביום המקדם 1.18 (תפוקה שולית יורדת). מגמת העבודה: א׳–ה׳. אפשר לשנות שעות, תאריך התחלה, משכים וחגים – התאריכים והגאנט מתעדכנים.</t>
+    <t>משכי הבסיס מחושבים לימי עבודה של 8 שעות. המשך בפועל = משך הבסיס ÷ מקדם התפוקה (מעוגל כלפי מעלה; משימות רשות/אישורים/ספקים/בדיקות קבועות אינן מוקטנות). ב-10 שעות ביום המקדם 1.18 (תפוקה שולית יורדת). מגמת העבודה: א׳–ה׳. אפשר לשנות שעות, תאריך התחלה, משכים וחגים – התאריכים והגאנט מתעדכנים.</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="15">
-        <f>IF(D13=0,0,MAX(1,ROUNDUP(D13/$D$5,0)))</f>
+        <f>D13</f>
         <v>0</v>
       </c>
       <c r="F13" s="15" t="s">
@@ -2471,7 +2471,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="15">
-        <f>IF(D14=0,0,MAX(1,ROUNDUP(D14/$D$5,0)))</f>
+        <f>D14</f>
         <v>3</v>
       </c>
       <c r="F14" s="15" t="s">
@@ -2513,8 +2513,8 @@
         <v>10</v>
       </c>
       <c r="E15" s="15">
-        <f>IF(D15=0,0,MAX(1,ROUNDUP(D15/$D$5,0)))</f>
-        <v>9</v>
+        <f>D15</f>
+        <v>10</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>65</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="N15" s="18">
         <f>IF(E15=0,M15,WORKDAY.INTL(M15,E15-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46345</v>
+        <v>46348</v>
       </c>
       <c r="O15" s="19" t="s">
         <v>68</v>
@@ -2557,8 +2557,8 @@
         <v>40</v>
       </c>
       <c r="E16" s="15">
-        <f>IF(D16=0,0,MAX(1,ROUNDUP(D16/$D$5,0)))</f>
-        <v>34</v>
+        <f>D16</f>
+        <v>40</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>65</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="N16" s="18">
         <f>IF(E16=0,M16,WORKDAY.INTL(M16,E16-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46380</v>
+        <v>46390</v>
       </c>
       <c r="O16" s="19"/>
       <c r="P16" s="15" t="s">
@@ -2599,8 +2599,8 @@
         <v>10</v>
       </c>
       <c r="E17" s="15">
-        <f>IF(D17=0,0,MAX(1,ROUNDUP(D17/$D$5,0)))</f>
-        <v>9</v>
+        <f>D17</f>
+        <v>10</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>65</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="N17" s="18">
         <f>IF(E17=0,M17,WORKDAY.INTL(M17,E17-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46345</v>
+        <v>46348</v>
       </c>
       <c r="O17" s="19"/>
       <c r="P17" s="15" t="s">
@@ -2641,8 +2641,8 @@
         <v>20</v>
       </c>
       <c r="E18" s="15">
-        <f>IF(D18=0,0,MAX(1,ROUNDUP(D18/$D$5,0)))</f>
-        <v>17</v>
+        <f>D18</f>
+        <v>20</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>82</v>
@@ -2654,15 +2654,15 @@
       <c r="K18" s="15"/>
       <c r="L18" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K18,$A$11:$A$86,0)),0))</f>
-        <v>46345</v>
+        <v>46348</v>
       </c>
       <c r="M18" s="18">
         <f>IF(E18=0,IF(COUNTA(F18:K18)=0,$D$2,L18),WORKDAY.INTL(L18,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46348</v>
+        <v>46349</v>
       </c>
       <c r="N18" s="18">
         <f>IF(E18=0,M18,WORKDAY.INTL(M18,E18-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46370</v>
+        <v>46376</v>
       </c>
       <c r="O18" s="19"/>
       <c r="P18" s="15" t="s">
@@ -2683,8 +2683,8 @@
         <v>20</v>
       </c>
       <c r="E19" s="15">
-        <f>IF(D19=0,0,MAX(1,ROUNDUP(D19/$D$5,0)))</f>
-        <v>17</v>
+        <f>D19</f>
+        <v>20</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>82</v>
@@ -2696,15 +2696,15 @@
       <c r="K19" s="15"/>
       <c r="L19" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K19,$A$11:$A$86,0)),0))</f>
-        <v>46345</v>
+        <v>46348</v>
       </c>
       <c r="M19" s="18">
         <f>IF(E19=0,IF(COUNTA(F19:K19)=0,$D$2,L19),WORKDAY.INTL(L19,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46348</v>
+        <v>46349</v>
       </c>
       <c r="N19" s="18">
         <f>IF(E19=0,M19,WORKDAY.INTL(M19,E19-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46370</v>
+        <v>46376</v>
       </c>
       <c r="O19" s="19"/>
       <c r="P19" s="15" t="s">
@@ -2830,15 +2830,15 @@
       <c r="K21" s="15"/>
       <c r="L21" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K21,$A$11:$A$86,0)),0))</f>
-        <v>46345</v>
+        <v>46348</v>
       </c>
       <c r="M21" s="18">
         <f>IF(E21=0,IF(COUNTA(F21:K21)=0,$D$2,L21),WORKDAY.INTL(L21,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46348</v>
+        <v>46349</v>
       </c>
       <c r="N21" s="18">
         <f>IF(E21=0,M21,WORKDAY.INTL(M21,E21-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46352</v>
+        <v>46355</v>
       </c>
       <c r="O21" s="19" t="s">
         <v>68</v>
@@ -2874,15 +2874,15 @@
       <c r="K22" s="15"/>
       <c r="L22" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K22,$A$11:$A$86,0)),0))</f>
-        <v>46352</v>
+        <v>46355</v>
       </c>
       <c r="M22" s="18">
         <f>IF(E22=0,IF(COUNTA(F22:K22)=0,$D$2,L22),WORKDAY.INTL(L22,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46355</v>
+        <v>46356</v>
       </c>
       <c r="N22" s="18">
         <f>IF(E22=0,M22,WORKDAY.INTL(M22,E22-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46358</v>
+        <v>46359</v>
       </c>
       <c r="O22" s="19" t="s">
         <v>68</v>
@@ -2905,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <f>IF(D23=0,0,MAX(1,ROUNDUP(D23/$D$5,0)))</f>
+        <f>D23</f>
         <v>1</v>
       </c>
       <c r="F23" s="15" t="s">
@@ -2918,15 +2918,15 @@
       <c r="K23" s="15"/>
       <c r="L23" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K23,$A$11:$A$86,0)),0))</f>
-        <v>46358</v>
+        <v>46359</v>
       </c>
       <c r="M23" s="18">
         <f>IF(E23=0,IF(COUNTA(F23:K23)=0,$D$2,L23),WORKDAY.INTL(L23,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46359</v>
+        <v>46362</v>
       </c>
       <c r="N23" s="18">
         <f>IF(E23=0,M23,WORKDAY.INTL(M23,E23-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46359</v>
+        <v>46362</v>
       </c>
       <c r="O23" s="19" t="s">
         <v>68</v>
@@ -3052,15 +3052,15 @@
       <c r="K25" s="15"/>
       <c r="L25" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K25,$A$11:$A$86,0)),0))</f>
-        <v>46359</v>
+        <v>46362</v>
       </c>
       <c r="M25" s="18">
         <f>IF(E25=0,IF(COUNTA(F25:K25)=0,$D$2,L25),WORKDAY.INTL(L25,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46362</v>
+        <v>46363</v>
       </c>
       <c r="N25" s="18">
         <f>IF(E25=0,M25,WORKDAY.INTL(M25,E25-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="O25" s="19" t="s">
         <v>68</v>
@@ -3096,15 +3096,15 @@
       <c r="K26" s="15"/>
       <c r="L26" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K26,$A$11:$A$86,0)),0))</f>
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="M26" s="18">
         <f>IF(E26=0,IF(COUNTA(F26:K26)=0,$D$2,L26),WORKDAY.INTL(L26,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46371</v>
+        <v>46372</v>
       </c>
       <c r="N26" s="18">
         <f>IF(E26=0,M26,WORKDAY.INTL(M26,E26-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46373</v>
+        <v>46376</v>
       </c>
       <c r="O26" s="19"/>
       <c r="P26" s="15" t="s">
@@ -3138,15 +3138,15 @@
       <c r="K27" s="15"/>
       <c r="L27" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K27,$A$11:$A$86,0)),0))</f>
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="M27" s="18">
         <f>IF(E27=0,IF(COUNTA(F27:K27)=0,$D$2,L27),WORKDAY.INTL(L27,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46371</v>
+        <v>46372</v>
       </c>
       <c r="N27" s="18">
         <f>IF(E27=0,M27,WORKDAY.INTL(M27,E27-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46373</v>
+        <v>46376</v>
       </c>
       <c r="O27" s="19"/>
       <c r="P27" s="15" t="s">
@@ -3180,15 +3180,15 @@
       <c r="K28" s="15"/>
       <c r="L28" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K28,$A$11:$A$86,0)),0))</f>
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="M28" s="18">
         <f>IF(E28=0,IF(COUNTA(F28:K28)=0,$D$2,L28),WORKDAY.INTL(L28,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46371</v>
+        <v>46372</v>
       </c>
       <c r="N28" s="18">
         <f>IF(E28=0,M28,WORKDAY.INTL(M28,E28-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46376</v>
+        <v>46377</v>
       </c>
       <c r="O28" s="19"/>
       <c r="P28" s="15" t="s">
@@ -3222,15 +3222,15 @@
       <c r="K29" s="15"/>
       <c r="L29" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K29,$A$11:$A$86,0)),0))</f>
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="M29" s="18">
         <f>IF(E29=0,IF(COUNTA(F29:K29)=0,$D$2,L29),WORKDAY.INTL(L29,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46371</v>
+        <v>46372</v>
       </c>
       <c r="N29" s="18">
         <f>IF(E29=0,M29,WORKDAY.INTL(M29,E29-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46378</v>
+        <v>46379</v>
       </c>
       <c r="O29" s="19" t="s">
         <v>68</v>
@@ -3268,15 +3268,15 @@
       <c r="K30" s="15"/>
       <c r="L30" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K30,$A$11:$A$86,0)),0))</f>
-        <v>46359</v>
+        <v>46362</v>
       </c>
       <c r="M30" s="18">
         <f>IF(E30=0,IF(COUNTA(F30:K30)=0,$D$2,L30),WORKDAY.INTL(L30,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46362</v>
+        <v>46363</v>
       </c>
       <c r="N30" s="18">
         <f>IF(E30=0,M30,WORKDAY.INTL(M30,E30-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46366</v>
+        <v>46369</v>
       </c>
       <c r="O30" s="19"/>
       <c r="P30" s="15" t="s">
@@ -3297,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="15">
-        <f>IF(D31=0,0,MAX(1,ROUNDUP(D31/$D$5,0)))</f>
+        <f>D31</f>
         <v>1</v>
       </c>
       <c r="F31" s="15" t="s">
@@ -3310,15 +3310,15 @@
       <c r="K31" s="15"/>
       <c r="L31" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K31,$A$11:$A$86,0)),0))</f>
-        <v>46366</v>
+        <v>46369</v>
       </c>
       <c r="M31" s="18">
         <f>IF(E31=0,IF(COUNTA(F31:K31)=0,$D$2,L31),WORKDAY.INTL(L31,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46369</v>
+        <v>46370</v>
       </c>
       <c r="N31" s="18">
         <f>IF(E31=0,M31,WORKDAY.INTL(M31,E31-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46369</v>
+        <v>46370</v>
       </c>
       <c r="O31" s="19"/>
       <c r="P31" s="15" t="s">
@@ -3356,15 +3356,15 @@
       <c r="K32" s="15"/>
       <c r="L32" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K32,$A$11:$A$86,0)),0))</f>
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="M32" s="18">
         <f>IF(E32=0,IF(COUNTA(F32:K32)=0,$D$2,L32),WORKDAY.INTL(L32,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46371</v>
+        <v>46372</v>
       </c>
       <c r="N32" s="18">
         <f>IF(E32=0,M32,WORKDAY.INTL(M32,E32-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46378</v>
+        <v>46379</v>
       </c>
       <c r="O32" s="19" t="s">
         <v>68</v>
@@ -3400,15 +3400,15 @@
       <c r="K33" s="15"/>
       <c r="L33" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K33,$A$11:$A$86,0)),0))</f>
-        <v>46359</v>
+        <v>46362</v>
       </c>
       <c r="M33" s="18">
         <f>IF(E33=0,IF(COUNTA(F33:K33)=0,$D$2,L33),WORKDAY.INTL(L33,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46362</v>
+        <v>46363</v>
       </c>
       <c r="N33" s="18">
         <f>IF(E33=0,M33,WORKDAY.INTL(M33,E33-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46369</v>
+        <v>46370</v>
       </c>
       <c r="O33" s="19"/>
       <c r="P33" s="15" t="s">
@@ -3452,15 +3452,15 @@
       </c>
       <c r="L34" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K34,$A$11:$A$86,0)),0))</f>
-        <v>46378</v>
+        <v>46379</v>
       </c>
       <c r="M34" s="18">
         <f>IF(E34=0,IF(COUNTA(F34:K34)=0,$D$2,L34),WORKDAY.INTL(L34,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46379</v>
+        <v>46380</v>
       </c>
       <c r="N34" s="18">
         <f>IF(E34=0,M34,WORKDAY.INTL(M34,E34-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46384</v>
+        <v>46385</v>
       </c>
       <c r="O34" s="19" t="s">
         <v>68</v>
@@ -3483,7 +3483,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="15">
-        <f>IF(D35=0,0,MAX(1,ROUNDUP(D35/$D$5,0)))</f>
+        <f>D35</f>
         <v>2</v>
       </c>
       <c r="F35" s="15" t="s">
@@ -3496,15 +3496,15 @@
       <c r="K35" s="15"/>
       <c r="L35" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K35,$A$11:$A$86,0)),0))</f>
-        <v>46384</v>
+        <v>46385</v>
       </c>
       <c r="M35" s="18">
         <f>IF(E35=0,IF(COUNTA(F35:K35)=0,$D$2,L35),WORKDAY.INTL(L35,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46385</v>
+        <v>46386</v>
       </c>
       <c r="N35" s="18">
         <f>IF(E35=0,M35,WORKDAY.INTL(M35,E35-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="O35" s="19" t="s">
         <v>68</v>
@@ -3630,15 +3630,15 @@
       <c r="K37" s="15"/>
       <c r="L37" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K37,$A$11:$A$86,0)),0))</f>
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="M37" s="18">
         <f>IF(E37=0,IF(COUNTA(F37:K37)=0,$D$2,L37),WORKDAY.INTL(L37,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46387</v>
+        <v>46390</v>
       </c>
       <c r="N37" s="18">
         <f>IF(E37=0,M37,WORKDAY.INTL(M37,E37-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46399</v>
+        <v>46400</v>
       </c>
       <c r="O37" s="19"/>
       <c r="P37" s="15" t="s">
@@ -3674,15 +3674,15 @@
       <c r="K38" s="15"/>
       <c r="L38" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K38,$A$11:$A$86,0)),0))</f>
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="M38" s="18">
         <f>IF(E38=0,IF(COUNTA(F38:K38)=0,$D$2,L38),WORKDAY.INTL(L38,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46387</v>
+        <v>46390</v>
       </c>
       <c r="N38" s="18">
         <f>IF(E38=0,M38,WORKDAY.INTL(M38,E38-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46405</v>
+        <v>46406</v>
       </c>
       <c r="O38" s="19"/>
       <c r="P38" s="15" t="s">
@@ -3716,15 +3716,15 @@
       <c r="K39" s="15"/>
       <c r="L39" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K39,$A$11:$A$86,0)),0))</f>
-        <v>46405</v>
+        <v>46406</v>
       </c>
       <c r="M39" s="18">
         <f>IF(E39=0,IF(COUNTA(F39:K39)=0,$D$2,L39),WORKDAY.INTL(L39,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46406</v>
+        <v>46407</v>
       </c>
       <c r="N39" s="18">
         <f>IF(E39=0,M39,WORKDAY.INTL(M39,E39-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46414</v>
+        <v>46415</v>
       </c>
       <c r="O39" s="19"/>
       <c r="P39" s="15" t="s">
@@ -3760,15 +3760,15 @@
       <c r="K40" s="15"/>
       <c r="L40" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K40,$A$11:$A$86,0)),0))</f>
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="M40" s="18">
         <f>IF(E40=0,IF(COUNTA(F40:K40)=0,$D$2,L40),WORKDAY.INTL(L40,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46387</v>
+        <v>46390</v>
       </c>
       <c r="N40" s="18">
         <f>IF(E40=0,M40,WORKDAY.INTL(M40,E40-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46420</v>
+        <v>46421</v>
       </c>
       <c r="O40" s="19"/>
       <c r="P40" s="15" t="s">
@@ -3804,15 +3804,15 @@
       <c r="K41" s="15"/>
       <c r="L41" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K41,$A$11:$A$86,0)),0))</f>
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="M41" s="18">
         <f>IF(E41=0,IF(COUNTA(F41:K41)=0,$D$2,L41),WORKDAY.INTL(L41,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46387</v>
+        <v>46390</v>
       </c>
       <c r="N41" s="18">
         <f>IF(E41=0,M41,WORKDAY.INTL(M41,E41-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46428</v>
+        <v>46429</v>
       </c>
       <c r="O41" s="19" t="s">
         <v>68</v>
@@ -3835,7 +3835,7 @@
         <v>2</v>
       </c>
       <c r="E42" s="15">
-        <f>IF(D42=0,0,MAX(1,ROUNDUP(D42/$D$5,0)))</f>
+        <f>D42</f>
         <v>2</v>
       </c>
       <c r="F42" s="15" t="s">
@@ -3856,15 +3856,15 @@
       <c r="K42" s="15"/>
       <c r="L42" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K42,$A$11:$A$86,0)),0))</f>
-        <v>46428</v>
+        <v>46429</v>
       </c>
       <c r="M42" s="18">
         <f>IF(E42=0,IF(COUNTA(F42:K42)=0,$D$2,L42),WORKDAY.INTL(L42,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46429</v>
+        <v>46432</v>
       </c>
       <c r="N42" s="18">
         <f>IF(E42=0,M42,WORKDAY.INTL(M42,E42-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="O42" s="19" t="s">
         <v>68</v>
@@ -3990,15 +3990,15 @@
       <c r="K44" s="15"/>
       <c r="L44" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K44,$A$11:$A$86,0)),0))</f>
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="M44" s="18">
         <f>IF(E44=0,IF(COUNTA(F44:K44)=0,$D$2,L44),WORKDAY.INTL(L44,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46387</v>
+        <v>46390</v>
       </c>
       <c r="N44" s="18">
         <f>IF(E44=0,M44,WORKDAY.INTL(M44,E44-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46392</v>
+        <v>46393</v>
       </c>
       <c r="O44" s="19"/>
       <c r="P44" s="15" t="s">
@@ -4034,15 +4034,15 @@
       <c r="K45" s="15"/>
       <c r="L45" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K45,$A$11:$A$86,0)),0))</f>
-        <v>46392</v>
+        <v>46393</v>
       </c>
       <c r="M45" s="18">
         <f>IF(E45=0,IF(COUNTA(F45:K45)=0,$D$2,L45),WORKDAY.INTL(L45,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46393</v>
+        <v>46394</v>
       </c>
       <c r="N45" s="18">
         <f>IF(E45=0,M45,WORKDAY.INTL(M45,E45-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46415</v>
+        <v>46418</v>
       </c>
       <c r="O45" s="19"/>
       <c r="P45" s="15" t="s">
@@ -4078,15 +4078,15 @@
       <c r="K46" s="15"/>
       <c r="L46" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K46,$A$11:$A$86,0)),0))</f>
-        <v>46392</v>
+        <v>46393</v>
       </c>
       <c r="M46" s="18">
         <f>IF(E46=0,IF(COUNTA(F46:K46)=0,$D$2,L46),WORKDAY.INTL(L46,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46393</v>
+        <v>46394</v>
       </c>
       <c r="N46" s="18">
         <f>IF(E46=0,M46,WORKDAY.INTL(M46,E46-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46415</v>
+        <v>46418</v>
       </c>
       <c r="O46" s="19"/>
       <c r="P46" s="15" t="s">
@@ -4107,7 +4107,7 @@
         <v>3</v>
       </c>
       <c r="E47" s="15">
-        <f>IF(D47=0,0,MAX(1,ROUNDUP(D47/$D$5,0)))</f>
+        <f>D47</f>
         <v>3</v>
       </c>
       <c r="F47" s="15" t="s">
@@ -4120,15 +4120,15 @@
       <c r="K47" s="15"/>
       <c r="L47" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K47,$A$11:$A$86,0)),0))</f>
-        <v>46415</v>
+        <v>46418</v>
       </c>
       <c r="M47" s="18">
         <f>IF(E47=0,IF(COUNTA(F47:K47)=0,$D$2,L47),WORKDAY.INTL(L47,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46418</v>
+        <v>46419</v>
       </c>
       <c r="N47" s="18">
         <f>IF(E47=0,M47,WORKDAY.INTL(M47,E47-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46420</v>
+        <v>46421</v>
       </c>
       <c r="O47" s="19"/>
       <c r="P47" s="15" t="s">
@@ -4149,7 +4149,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="15">
-        <f>IF(D48=0,0,MAX(1,ROUNDUP(D48/$D$5,0)))</f>
+        <f>D48</f>
         <v>3</v>
       </c>
       <c r="F48" s="15" t="s">
@@ -4162,15 +4162,15 @@
       <c r="K48" s="15"/>
       <c r="L48" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K48,$A$11:$A$86,0)),0))</f>
-        <v>46415</v>
+        <v>46418</v>
       </c>
       <c r="M48" s="18">
         <f>IF(E48=0,IF(COUNTA(F48:K48)=0,$D$2,L48),WORKDAY.INTL(L48,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46418</v>
+        <v>46419</v>
       </c>
       <c r="N48" s="18">
         <f>IF(E48=0,M48,WORKDAY.INTL(M48,E48-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46420</v>
+        <v>46421</v>
       </c>
       <c r="O48" s="19"/>
       <c r="P48" s="15" t="s">
@@ -4298,15 +4298,15 @@
       <c r="K50" s="15"/>
       <c r="L50" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K50,$A$11:$A$86,0)),0))</f>
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="M50" s="18">
         <f>IF(E50=0,IF(COUNTA(F50:K50)=0,$D$2,L50),WORKDAY.INTL(L50,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46433</v>
+        <v>46434</v>
       </c>
       <c r="N50" s="18">
         <f>IF(E50=0,M50,WORKDAY.INTL(M50,E50-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46447</v>
+        <v>46448</v>
       </c>
       <c r="O50" s="19" t="s">
         <v>68</v>
@@ -4342,15 +4342,15 @@
       <c r="K51" s="15"/>
       <c r="L51" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K51,$A$11:$A$86,0)),0))</f>
-        <v>46447</v>
+        <v>46448</v>
       </c>
       <c r="M51" s="18">
         <f>IF(E51=0,IF(COUNTA(F51:K51)=0,$D$2,L51),WORKDAY.INTL(L51,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46448</v>
+        <v>46449</v>
       </c>
       <c r="N51" s="18">
         <f>IF(E51=0,M51,WORKDAY.INTL(M51,E51-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46455</v>
+        <v>46456</v>
       </c>
       <c r="O51" s="19" t="s">
         <v>68</v>
@@ -4373,7 +4373,7 @@
         <v>2</v>
       </c>
       <c r="E52" s="15">
-        <f>IF(D52=0,0,MAX(1,ROUNDUP(D52/$D$5,0)))</f>
+        <f>D52</f>
         <v>2</v>
       </c>
       <c r="F52" s="15" t="s">
@@ -4386,15 +4386,15 @@
       <c r="K52" s="15"/>
       <c r="L52" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K52,$A$11:$A$86,0)),0))</f>
-        <v>46455</v>
+        <v>46456</v>
       </c>
       <c r="M52" s="18">
         <f>IF(E52=0,IF(COUNTA(F52:K52)=0,$D$2,L52),WORKDAY.INTL(L52,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46456</v>
+        <v>46457</v>
       </c>
       <c r="N52" s="18">
         <f>IF(E52=0,M52,WORKDAY.INTL(M52,E52-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46457</v>
+        <v>46460</v>
       </c>
       <c r="O52" s="19" t="s">
         <v>68</v>
@@ -4432,15 +4432,15 @@
       <c r="K53" s="15"/>
       <c r="L53" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K53,$A$11:$A$86,0)),0))</f>
-        <v>46420</v>
+        <v>46421</v>
       </c>
       <c r="M53" s="18">
         <f>IF(E53=0,IF(COUNTA(F53:K53)=0,$D$2,L53),WORKDAY.INTL(L53,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46421</v>
+        <v>46422</v>
       </c>
       <c r="N53" s="18">
         <f>IF(E53=0,M53,WORKDAY.INTL(M53,E53-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46428</v>
+        <v>46429</v>
       </c>
       <c r="O53" s="19"/>
       <c r="P53" s="15" t="s">
@@ -4476,15 +4476,15 @@
       <c r="K54" s="15"/>
       <c r="L54" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K54,$A$11:$A$86,0)),0))</f>
-        <v>46420</v>
+        <v>46421</v>
       </c>
       <c r="M54" s="18">
         <f>IF(E54=0,IF(COUNTA(F54:K54)=0,$D$2,L54),WORKDAY.INTL(L54,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46421</v>
+        <v>46422</v>
       </c>
       <c r="N54" s="18">
         <f>IF(E54=0,M54,WORKDAY.INTL(M54,E54-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46428</v>
+        <v>46429</v>
       </c>
       <c r="O54" s="19"/>
       <c r="P54" s="15" t="s">
@@ -4505,7 +4505,7 @@
         <v>3</v>
       </c>
       <c r="E55" s="15">
-        <f>IF(D55=0,0,MAX(1,ROUNDUP(D55/$D$5,0)))</f>
+        <f>D55</f>
         <v>3</v>
       </c>
       <c r="F55" s="15" t="s">
@@ -4520,15 +4520,15 @@
       <c r="K55" s="15"/>
       <c r="L55" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K55,$A$11:$A$86,0)),0))</f>
-        <v>46428</v>
+        <v>46429</v>
       </c>
       <c r="M55" s="18">
         <f>IF(E55=0,IF(COUNTA(F55:K55)=0,$D$2,L55),WORKDAY.INTL(L55,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46429</v>
+        <v>46432</v>
       </c>
       <c r="N55" s="18">
         <f>IF(E55=0,M55,WORKDAY.INTL(M55,E55-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46433</v>
+        <v>46434</v>
       </c>
       <c r="O55" s="19"/>
       <c r="P55" s="15" t="s">
@@ -4549,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="15">
-        <f>IF(D56=0,0,MAX(1,ROUNDUP(D56/$D$5,0)))</f>
+        <f>D56</f>
         <v>1</v>
       </c>
       <c r="F56" s="15" t="s">
@@ -4562,15 +4562,15 @@
       <c r="K56" s="15"/>
       <c r="L56" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K56,$A$11:$A$86,0)),0))</f>
-        <v>46433</v>
+        <v>46434</v>
       </c>
       <c r="M56" s="18">
         <f>IF(E56=0,IF(COUNTA(F56:K56)=0,$D$2,L56),WORKDAY.INTL(L56,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46434</v>
+        <v>46435</v>
       </c>
       <c r="N56" s="18">
         <f>IF(E56=0,M56,WORKDAY.INTL(M56,E56-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46434</v>
+        <v>46435</v>
       </c>
       <c r="O56" s="19"/>
       <c r="P56" s="15" t="s">
@@ -4681,8 +4681,8 @@
         <v>40</v>
       </c>
       <c r="E58" s="15">
-        <f>IF(D58=0,0,MAX(1,ROUNDUP(D58/$D$5,0)))</f>
-        <v>34</v>
+        <f>D58</f>
+        <v>40</v>
       </c>
       <c r="F58" s="15" t="s">
         <v>130</v>
@@ -4694,15 +4694,15 @@
       <c r="K58" s="15"/>
       <c r="L58" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K58,$A$11:$A$86,0)),0))</f>
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="M58" s="18">
         <f>IF(E58=0,IF(COUNTA(F58:K58)=0,$D$2,L58),WORKDAY.INTL(L58,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46387</v>
+        <v>46390</v>
       </c>
       <c r="N58" s="18">
         <f>IF(E58=0,M58,WORKDAY.INTL(M58,E58-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46434</v>
+        <v>46443</v>
       </c>
       <c r="O58" s="19"/>
       <c r="P58" s="15" t="s">
@@ -4740,15 +4740,15 @@
       <c r="K59" s="15"/>
       <c r="L59" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K59,$A$11:$A$86,0)),0))</f>
-        <v>46434</v>
+        <v>46443</v>
       </c>
       <c r="M59" s="18">
         <f>IF(E59=0,IF(COUNTA(F59:K59)=0,$D$2,L59),WORKDAY.INTL(L59,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46435</v>
+        <v>46446</v>
       </c>
       <c r="N59" s="18">
         <f>IF(E59=0,M59,WORKDAY.INTL(M59,E59-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46457</v>
+        <v>46468</v>
       </c>
       <c r="O59" s="19"/>
       <c r="P59" s="15" t="s">
@@ -4784,15 +4784,15 @@
       <c r="K60" s="15"/>
       <c r="L60" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K60,$A$11:$A$86,0)),0))</f>
-        <v>46457</v>
+        <v>46468</v>
       </c>
       <c r="M60" s="18">
         <f>IF(E60=0,IF(COUNTA(F60:K60)=0,$D$2,L60),WORKDAY.INTL(L60,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46460</v>
+        <v>46469</v>
       </c>
       <c r="N60" s="18">
         <f>IF(E60=0,M60,WORKDAY.INTL(M60,E60-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46468</v>
+        <v>46477</v>
       </c>
       <c r="O60" s="19"/>
       <c r="P60" s="15" t="s">
@@ -4828,15 +4828,15 @@
       <c r="K61" s="15"/>
       <c r="L61" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K61,$A$11:$A$86,0)),0))</f>
-        <v>46468</v>
+        <v>46477</v>
       </c>
       <c r="M61" s="18">
         <f>IF(E61=0,IF(COUNTA(F61:K61)=0,$D$2,L61),WORKDAY.INTL(L61,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46469</v>
+        <v>46478</v>
       </c>
       <c r="N61" s="18">
         <f>IF(E61=0,M61,WORKDAY.INTL(M61,E61-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46474</v>
+        <v>46483</v>
       </c>
       <c r="O61" s="19"/>
       <c r="P61" s="15" t="s">
@@ -4962,15 +4962,15 @@
       <c r="K63" s="15"/>
       <c r="L63" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K63,$A$11:$A$86,0)),0))</f>
-        <v>46457</v>
+        <v>46460</v>
       </c>
       <c r="M63" s="18">
         <f>IF(E63=0,IF(COUNTA(F63:K63)=0,$D$2,L63),WORKDAY.INTL(L63,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46460</v>
+        <v>46461</v>
       </c>
       <c r="N63" s="18">
         <f>IF(E63=0,M63,WORKDAY.INTL(M63,E63-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46474</v>
+        <v>46475</v>
       </c>
       <c r="O63" s="19"/>
       <c r="P63" s="15" t="s">
@@ -5008,15 +5008,15 @@
       <c r="K64" s="15"/>
       <c r="L64" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K64,$A$11:$A$86,0)),0))</f>
-        <v>46457</v>
+        <v>46460</v>
       </c>
       <c r="M64" s="18">
         <f>IF(E64=0,IF(COUNTA(F64:K64)=0,$D$2,L64),WORKDAY.INTL(L64,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46460</v>
+        <v>46461</v>
       </c>
       <c r="N64" s="18">
         <f>IF(E64=0,M64,WORKDAY.INTL(M64,E64-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46475</v>
+        <v>46476</v>
       </c>
       <c r="O64" s="19" t="s">
         <v>68</v>
@@ -5054,15 +5054,15 @@
       <c r="K65" s="15"/>
       <c r="L65" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K65,$A$11:$A$86,0)),0))</f>
-        <v>46434</v>
+        <v>46435</v>
       </c>
       <c r="M65" s="18">
         <f>IF(E65=0,IF(COUNTA(F65:K65)=0,$D$2,L65),WORKDAY.INTL(L65,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46435</v>
+        <v>46436</v>
       </c>
       <c r="N65" s="18">
         <f>IF(E65=0,M65,WORKDAY.INTL(M65,E65-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46443</v>
+        <v>46446</v>
       </c>
       <c r="O65" s="19"/>
       <c r="P65" s="15" t="s">
@@ -5098,15 +5098,15 @@
       <c r="K66" s="15"/>
       <c r="L66" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K66,$A$11:$A$86,0)),0))</f>
-        <v>46433</v>
+        <v>46434</v>
       </c>
       <c r="M66" s="18">
         <f>IF(E66=0,IF(COUNTA(F66:K66)=0,$D$2,L66),WORKDAY.INTL(L66,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46434</v>
+        <v>46435</v>
       </c>
       <c r="N66" s="18">
         <f>IF(E66=0,M66,WORKDAY.INTL(M66,E66-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46453</v>
+        <v>46454</v>
       </c>
       <c r="O66" s="19"/>
       <c r="P66" s="15" t="s">
@@ -5146,15 +5146,15 @@
       <c r="K67" s="15"/>
       <c r="L67" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K67,$A$11:$A$86,0)),0))</f>
-        <v>46475</v>
+        <v>46476</v>
       </c>
       <c r="M67" s="18">
         <f>IF(E67=0,IF(COUNTA(F67:K67)=0,$D$2,L67),WORKDAY.INTL(L67,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46476</v>
+        <v>46477</v>
       </c>
       <c r="N67" s="18">
         <f>IF(E67=0,M67,WORKDAY.INTL(M67,E67-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46484</v>
+        <v>46485</v>
       </c>
       <c r="O67" s="19"/>
       <c r="P67" s="15" t="s">
@@ -5192,15 +5192,15 @@
       <c r="K68" s="15"/>
       <c r="L68" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K68,$A$11:$A$86,0)),0))</f>
-        <v>46475</v>
+        <v>46476</v>
       </c>
       <c r="M68" s="18">
         <f>IF(E68=0,IF(COUNTA(F68:K68)=0,$D$2,L68),WORKDAY.INTL(L68,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46476</v>
+        <v>46477</v>
       </c>
       <c r="N68" s="18">
         <f>IF(E68=0,M68,WORKDAY.INTL(M68,E68-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46490</v>
+        <v>46491</v>
       </c>
       <c r="O68" s="19" t="s">
         <v>68</v>
@@ -5242,15 +5242,15 @@
       <c r="K69" s="15"/>
       <c r="L69" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K69,$A$11:$A$86,0)),0))</f>
-        <v>46490</v>
+        <v>46491</v>
       </c>
       <c r="M69" s="18">
         <f>IF(E69=0,IF(COUNTA(F69:K69)=0,$D$2,L69),WORKDAY.INTL(L69,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46491</v>
+        <v>46492</v>
       </c>
       <c r="N69" s="18">
         <f>IF(E69=0,M69,WORKDAY.INTL(M69,E69-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46516</v>
+        <v>46517</v>
       </c>
       <c r="O69" s="19" t="s">
         <v>68</v>
@@ -5286,15 +5286,15 @@
       <c r="K70" s="15"/>
       <c r="L70" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K70,$A$11:$A$86,0)),0))</f>
-        <v>46516</v>
+        <v>46517</v>
       </c>
       <c r="M70" s="18">
         <f>IF(E70=0,IF(COUNTA(F70:K70)=0,$D$2,L70),WORKDAY.INTL(L70,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46517</v>
+        <v>46518</v>
       </c>
       <c r="N70" s="18">
         <f>IF(E70=0,M70,WORKDAY.INTL(M70,E70-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46526</v>
+        <v>46527</v>
       </c>
       <c r="O70" s="19"/>
       <c r="P70" s="15" t="s">
@@ -5328,15 +5328,15 @@
       <c r="K71" s="15"/>
       <c r="L71" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K71,$A$11:$A$86,0)),0))</f>
-        <v>46516</v>
+        <v>46517</v>
       </c>
       <c r="M71" s="18">
         <f>IF(E71=0,IF(COUNTA(F71:K71)=0,$D$2,L71),WORKDAY.INTL(L71,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46517</v>
+        <v>46518</v>
       </c>
       <c r="N71" s="18">
         <f>IF(E71=0,M71,WORKDAY.INTL(M71,E71-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46520</v>
+        <v>46523</v>
       </c>
       <c r="O71" s="19"/>
       <c r="P71" s="15" t="s">
@@ -5374,15 +5374,15 @@
       <c r="K72" s="15"/>
       <c r="L72" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K72,$A$11:$A$86,0)),0))</f>
-        <v>46516</v>
+        <v>46517</v>
       </c>
       <c r="M72" s="18">
         <f>IF(E72=0,IF(COUNTA(F72:K72)=0,$D$2,L72),WORKDAY.INTL(L72,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46517</v>
+        <v>46518</v>
       </c>
       <c r="N72" s="18">
         <f>IF(E72=0,M72,WORKDAY.INTL(M72,E72-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46526</v>
+        <v>46527</v>
       </c>
       <c r="O72" s="19" t="s">
         <v>68</v>
@@ -5510,15 +5510,15 @@
       <c r="K74" s="15"/>
       <c r="L74" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K74,$A$11:$A$86,0)),0))</f>
-        <v>46380</v>
+        <v>46390</v>
       </c>
       <c r="M74" s="18">
         <f>IF(E74=0,IF(COUNTA(F74:K74)=0,$D$2,L74),WORKDAY.INTL(L74,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46383</v>
+        <v>46391</v>
       </c>
       <c r="N74" s="18">
         <f>IF(E74=0,M74,WORKDAY.INTL(M74,E74-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46387</v>
+        <v>46397</v>
       </c>
       <c r="O74" s="19"/>
       <c r="P74" s="15" t="s">
@@ -5552,15 +5552,15 @@
       <c r="K75" s="15"/>
       <c r="L75" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K75,$A$11:$A$86,0)),0))</f>
-        <v>46457</v>
+        <v>46468</v>
       </c>
       <c r="M75" s="18">
         <f>IF(E75=0,IF(COUNTA(F75:K75)=0,$D$2,L75),WORKDAY.INTL(L75,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46460</v>
+        <v>46469</v>
       </c>
       <c r="N75" s="18">
         <f>IF(E75=0,M75,WORKDAY.INTL(M75,E75-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46469</v>
+        <v>46478</v>
       </c>
       <c r="O75" s="19"/>
       <c r="P75" s="15" t="s">
@@ -5594,15 +5594,15 @@
       <c r="K76" s="15"/>
       <c r="L76" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K76,$A$11:$A$86,0)),0))</f>
-        <v>46469</v>
+        <v>46478</v>
       </c>
       <c r="M76" s="18">
         <f>IF(E76=0,IF(COUNTA(F76:K76)=0,$D$2,L76),WORKDAY.INTL(L76,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46470</v>
+        <v>46481</v>
       </c>
       <c r="N76" s="18">
         <f>IF(E76=0,M76,WORKDAY.INTL(M76,E76-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46477</v>
+        <v>46488</v>
       </c>
       <c r="O76" s="19"/>
       <c r="P76" s="15" t="s">
@@ -5638,15 +5638,15 @@
       <c r="K77" s="15"/>
       <c r="L77" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K77,$A$11:$A$86,0)),0))</f>
-        <v>46477</v>
+        <v>46488</v>
       </c>
       <c r="M77" s="18">
         <f>IF(E77=0,IF(COUNTA(F77:K77)=0,$D$2,L77),WORKDAY.INTL(L77,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46478</v>
+        <v>46489</v>
       </c>
       <c r="N77" s="18">
         <f>IF(E77=0,M77,WORKDAY.INTL(M77,E77-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46491</v>
+        <v>46509</v>
       </c>
       <c r="O77" s="19"/>
       <c r="P77" s="15" t="s">
@@ -5776,15 +5776,15 @@
       <c r="K79" s="15"/>
       <c r="L79" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K79,$A$11:$A$86,0)),0))</f>
-        <v>46526</v>
+        <v>46527</v>
       </c>
       <c r="M79" s="18">
         <f>IF(E79=0,IF(COUNTA(F79:K79)=0,$D$2,L79),WORKDAY.INTL(L79,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46527</v>
+        <v>46530</v>
       </c>
       <c r="N79" s="18">
         <f>IF(E79=0,M79,WORKDAY.INTL(M79,E79-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46531</v>
+        <v>46532</v>
       </c>
       <c r="O79" s="19"/>
       <c r="P79" s="15" t="s">
@@ -5818,15 +5818,15 @@
       <c r="K80" s="15"/>
       <c r="L80" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K80,$A$11:$A$86,0)),0))</f>
-        <v>46526</v>
+        <v>46527</v>
       </c>
       <c r="M80" s="18">
         <f>IF(E80=0,IF(COUNTA(F80:K80)=0,$D$2,L80),WORKDAY.INTL(L80,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46527</v>
+        <v>46530</v>
       </c>
       <c r="N80" s="18">
         <f>IF(E80=0,M80,WORKDAY.INTL(M80,E80-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46532</v>
+        <v>46533</v>
       </c>
       <c r="O80" s="19" t="s">
         <v>68</v>
@@ -5870,15 +5870,15 @@
       <c r="K81" s="15"/>
       <c r="L81" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K81,$A$11:$A$86,0)),0))</f>
-        <v>46526</v>
+        <v>46527</v>
       </c>
       <c r="M81" s="18">
         <f>IF(E81=0,IF(COUNTA(F81:K81)=0,$D$2,L81),WORKDAY.INTL(L81,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46527</v>
+        <v>46530</v>
       </c>
       <c r="N81" s="18">
         <f>IF(E81=0,M81,WORKDAY.INTL(M81,E81-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46531</v>
+        <v>46532</v>
       </c>
       <c r="O81" s="19"/>
       <c r="P81" s="15" t="s">
@@ -5899,7 +5899,7 @@
         <v>3</v>
       </c>
       <c r="E82" s="15">
-        <f>IF(D82=0,0,MAX(1,ROUNDUP(D82/$D$5,0)))</f>
+        <f>D82</f>
         <v>3</v>
       </c>
       <c r="F82" s="15" t="s">
@@ -5916,15 +5916,15 @@
       <c r="K82" s="15"/>
       <c r="L82" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K82,$A$11:$A$86,0)),0))</f>
-        <v>46532</v>
+        <v>46533</v>
       </c>
       <c r="M82" s="18">
         <f>IF(E82=0,IF(COUNTA(F82:K82)=0,$D$2,L82),WORKDAY.INTL(L82,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46533</v>
+        <v>46534</v>
       </c>
       <c r="N82" s="18">
         <f>IF(E82=0,M82,WORKDAY.INTL(M82,E82-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46537</v>
+        <v>46538</v>
       </c>
       <c r="O82" s="19" t="s">
         <v>68</v>
@@ -5960,15 +5960,15 @@
       <c r="K83" s="15"/>
       <c r="L83" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K83,$A$11:$A$86,0)),0))</f>
-        <v>46537</v>
+        <v>46538</v>
       </c>
       <c r="M83" s="18">
         <f>IF(E83=0,IF(COUNTA(F83:K83)=0,$D$2,L83),WORKDAY.INTL(L83,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46538</v>
+        <v>46539</v>
       </c>
       <c r="N83" s="18">
         <f>IF(E83=0,M83,WORKDAY.INTL(M83,E83-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46546</v>
+        <v>46547</v>
       </c>
       <c r="O83" s="19"/>
       <c r="P83" s="15" t="s">
@@ -5989,8 +5989,8 @@
         <v>10</v>
       </c>
       <c r="E84" s="15">
-        <f>IF(D84=0,0,MAX(1,ROUNDUP(D84/$D$5,0)))</f>
-        <v>9</v>
+        <f>D84</f>
+        <v>10</v>
       </c>
       <c r="F84" s="15" t="s">
         <v>247</v>
@@ -6002,15 +6002,15 @@
       <c r="K84" s="15"/>
       <c r="L84" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K84,$A$11:$A$86,0)),0))</f>
-        <v>46537</v>
+        <v>46538</v>
       </c>
       <c r="M84" s="18">
         <f>IF(E84=0,IF(COUNTA(F84:K84)=0,$D$2,L84),WORKDAY.INTL(L84,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46538</v>
+        <v>46539</v>
       </c>
       <c r="N84" s="18">
         <f>IF(E84=0,M84,WORKDAY.INTL(M84,E84-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46548</v>
+        <v>46552</v>
       </c>
       <c r="O84" s="19" t="s">
         <v>68</v>
@@ -6046,15 +6046,15 @@
       <c r="K85" s="15"/>
       <c r="L85" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K85,$A$11:$A$86,0)),0))</f>
-        <v>46546</v>
+        <v>46547</v>
       </c>
       <c r="M85" s="18">
         <f>IF(E85=0,IF(COUNTA(F85:K85)=0,$D$2,L85),WORKDAY.INTL(L85,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46546</v>
+        <v>46547</v>
       </c>
       <c r="N85" s="18">
         <f>IF(E85=0,M85,WORKDAY.INTL(M85,E85-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46546</v>
+        <v>46547</v>
       </c>
       <c r="O85" s="19"/>
       <c r="P85" s="15" t="s">
@@ -6075,8 +6075,8 @@
         <v>30</v>
       </c>
       <c r="E86" s="15">
-        <f>IF(D86=0,0,MAX(1,ROUNDUP(D86/$D$5,0)))</f>
-        <v>26</v>
+        <f>D86</f>
+        <v>30</v>
       </c>
       <c r="F86" s="15" t="s">
         <v>251</v>
@@ -6090,15 +6090,15 @@
       <c r="K86" s="15"/>
       <c r="L86" s="18">
         <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K86,$A$11:$A$86,0)),0))</f>
-        <v>46548</v>
+        <v>46552</v>
       </c>
       <c r="M86" s="18">
         <f>IF(E86=0,IF(COUNTA(F86:K86)=0,$D$2,L86),WORKDAY.INTL(L86,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46551</v>
+        <v>46553</v>
       </c>
       <c r="N86" s="18">
         <f>IF(E86=0,M86,WORKDAY.INTL(M86,E86-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46586</v>
+        <v>46594</v>
       </c>
       <c r="O86" s="19"/>
       <c r="P86" s="15" t="s">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="N88" s="20">
         <f>N85</f>
-        <v>46546</v>
+        <v>46547</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="N89" s="20">
         <f>N86</f>
-        <v>46586</v>
+        <v>46594</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="N90" s="21">
         <f>ROUND((N88-$D$2+1)/7,1)</f>
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="N91" s="21">
         <f>NETWORKDAYS.INTL($D$2,N88,$D$3,'לוח שנה וחגים'!$F$5:$F$20)</f>
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="92" spans="1:16">

--- a/05_תוצרים/לוח_זמנים_שלונסקי_53_ישראל_פועלים_סינים.xlsx
+++ b/05_תוצרים/לוח_זמנים_שלונסקי_53_ישראל_פועלים_סינים.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="318">
   <si>
     <t>לוח שנה וחגים – ישראל (תשפ"ז, נובמבר 2026 – יולי 2027)</t>
   </si>
@@ -277,6 +277,24 @@
     <t>14.01</t>
   </si>
   <si>
+    <t>A035</t>
+  </si>
+  <si>
+    <t>אישור יועץ האיטום לשיטת העבודה (לפני תחילת איטום)</t>
+  </si>
+  <si>
+    <t>10.01, 10.04</t>
+  </si>
+  <si>
+    <t>A040</t>
+  </si>
+  <si>
+    <t>החלטת המזמין הסופית בכתב על תריסים חשמליים (תנאי להנחת תשתית חשמל)</t>
+  </si>
+  <si>
+    <t>06.03</t>
+  </si>
+  <si>
     <t>A050</t>
   </si>
   <si>
@@ -301,10 +319,10 @@
     <t>S010</t>
   </si>
   <si>
-    <t>התארגנות אתר, גידור, חיבורי מים וחשמל זמניים, מכולת פסולת</t>
-  </si>
-  <si>
-    <t>01.01–01.04, 01.07</t>
+    <t>התארגנות אתר, גידור, חיבורי מים וחשמל זמניים, מכולת פסולת וניקיון שוטף</t>
+  </si>
+  <si>
+    <t>01.01–01.04, 01.07, 01.08</t>
   </si>
   <si>
     <t>S020</t>
@@ -319,7 +337,7 @@
     <t>S030</t>
   </si>
   <si>
-    <t>אישור כתוב של המתכננת למעבר להריסות</t>
+    <t>אישור כתוב של המתכננת והקונסטרוקטור למעבר להריסות (כולל סימון האלמנטים להריסה)</t>
   </si>
   <si>
     <t>הריסות ופירוקים</t>
@@ -331,7 +349,7 @@
     <t>פירוק חלונות, דלתות, כלים סניטריים, ארונות, מיזוג, חשמל וצנרת גלויה</t>
   </si>
   <si>
-    <t>02.06–02.13</t>
+    <t>02.06–02.14</t>
   </si>
   <si>
     <t>D020</t>
@@ -457,6 +475,12 @@
     <t>03.01</t>
   </si>
   <si>
+    <t>K035</t>
+  </si>
+  <si>
+    <t>בדיקת ריתוכי שלד הפלדה (פרגולה) על ידי בודק ריתוכים מוסמך</t>
+  </si>
+  <si>
     <t>K040</t>
   </si>
   <si>
@@ -502,6 +526,15 @@
     <t>06.01–06.06, 06.10, 06.11, 07.11, 07.20</t>
   </si>
   <si>
+    <t>EXT2</t>
+  </si>
+  <si>
+    <t>על ידי אחרים: צנרת מיזוג וניקוז ותשתית תקשורת, מיגון ושמע (לפני סגירת גבס)</t>
+  </si>
+  <si>
+    <t>(מחוץ להיקף)</t>
+  </si>
+  <si>
     <t>Q010</t>
   </si>
   <si>
@@ -583,13 +616,10 @@
     <t>חזית ופיתוח חיצוני</t>
   </si>
   <si>
-    <t>EXT1</t>
-  </si>
-  <si>
-    <t>על ידי אחרים: אלומיניום ודלתות – אספקה והתקנה</t>
-  </si>
-  <si>
-    <t>(מחוץ להיקף)</t>
+    <t>EXT5</t>
+  </si>
+  <si>
+    <t>על ידי אחרים: פרפט, איטום וקופינג בגג (פרק 11 במפרט – מחוץ להיקף)</t>
   </si>
   <si>
     <t>X020</t>
@@ -598,13 +628,34 @@
     <t>הכנת תשתית וטיח צבעוני לחזיתות (225 מ"ר)</t>
   </si>
   <si>
-    <t>Z010</t>
-  </si>
-  <si>
-    <t>אדני חלונות ואיטום חלונות</t>
-  </si>
-  <si>
-    <t>12.01, 12.02, 12.04</t>
+    <t>EXT1a</t>
+  </si>
+  <si>
+    <t>מדידה סופית בשטח לאחר טיח חיצוני ואישור לוח האלומיניום והדלתות (המזמין/ספק)</t>
+  </si>
+  <si>
+    <t>EXT1b</t>
+  </si>
+  <si>
+    <t>על ידי אחרים: אספקה והתקנת אלומיניום (R1–R26), דלתות ושערים</t>
+  </si>
+  <si>
+    <t>Z010a</t>
+  </si>
+  <si>
+    <t>אדני חלונות פנימיים וחיצוניים (לאחר אישור לוח האלומיניום)</t>
+  </si>
+  <si>
+    <t>12.01, 12.02</t>
+  </si>
+  <si>
+    <t>Z010b</t>
+  </si>
+  <si>
+    <t>איטום חלונות ובדיקת מים לספי חוץ (לאחר התקנת האלומיניום)</t>
+  </si>
+  <si>
+    <t>12.04</t>
   </si>
   <si>
     <t>X030</t>
@@ -628,13 +679,19 @@
     <t>T010</t>
   </si>
   <si>
+    <t>T020</t>
+  </si>
+  <si>
+    <t>EXT3</t>
+  </si>
+  <si>
+    <t>על ידי אחרים: התקנת יחידות מיזוג, בדיקות ואקום ולחץ ואישור המיזוג (לפני טיח וצבע בחדר)</t>
+  </si>
+  <si>
     <t>ריצוף פנים 120×120 ו-120×60 ס"מ</t>
   </si>
   <si>
     <t>13.01, 13.02</t>
-  </si>
-  <si>
-    <t>T020</t>
   </si>
   <si>
     <t>חיפוי קירות מקלחות (121 מ"ר)</t>
@@ -1504,7 +1561,7 @@
     <tabColor rgb="FF0038B8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CI93"/>
+  <dimension ref="A1:CI101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -2397,7 +2454,7 @@
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
       <c r="L12" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F12,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G12,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H12,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I12,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J12,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K12,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F12,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G12,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H12,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I12,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J12,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K12,$A$11:$A$94,0)),0))</f>
         <v>46333</v>
       </c>
       <c r="M12" s="18">
@@ -2441,7 +2498,7 @@
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
       <c r="L13" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F13,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G13,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H13,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I13,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J13,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K13,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F13,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G13,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H13,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I13,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J13,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K13,$A$11:$A$94,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M13" s="18">
@@ -2483,7 +2540,7 @@
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
       <c r="L14" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F14,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G14,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H14,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I14,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J14,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K14,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F14,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G14,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H14,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I14,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J14,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K14,$A$11:$A$94,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M14" s="18">
@@ -2525,7 +2582,7 @@
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
       <c r="L15" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F15,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G15,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H15,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I15,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J15,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K15,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F15,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G15,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H15,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I15,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J15,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K15,$A$11:$A$94,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M15" s="18">
@@ -2569,7 +2626,7 @@
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
       <c r="L16" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F16,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G16,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H16,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I16,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J16,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K16,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F16,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G16,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H16,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I16,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J16,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K16,$A$11:$A$94,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M16" s="18">
@@ -2611,7 +2668,7 @@
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
       <c r="L17" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F17,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G17,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H17,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I17,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J17,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K17,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F17,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G17,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H17,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I17,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J17,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K17,$A$11:$A$94,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M17" s="18">
@@ -2638,14 +2695,14 @@
         <v>87</v>
       </c>
       <c r="D18" s="17">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
         <f>D18</f>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
@@ -2653,23 +2710,23 @@
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
       <c r="L18" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J18,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K18,$A$11:$A$86,0)),0))</f>
-        <v>46348</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F18,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G18,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H18,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I18,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J18,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K18,$A$11:$A$94,0)),0))</f>
+        <v>46334</v>
       </c>
       <c r="M18" s="18">
         <f>IF(E18=0,IF(COUNTA(F18:K18)=0,$D$2,L18),WORKDAY.INTL(L18,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46349</v>
+        <v>46335</v>
       </c>
       <c r="N18" s="18">
         <f>IF(E18=0,M18,WORKDAY.INTL(M18,E18-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46376</v>
+        <v>46337</v>
       </c>
       <c r="O18" s="19"/>
       <c r="P18" s="15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:87">
+    <row r="19" spans="1:87" ht="26" customHeight="1">
       <c r="A19" s="15" t="s">
         <v>88</v>
       </c>
@@ -2680,14 +2737,14 @@
         <v>90</v>
       </c>
       <c r="D19" s="17">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
         <f>D19</f>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
@@ -2695,16 +2752,16 @@
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J19,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K19,$A$11:$A$86,0)),0))</f>
-        <v>46348</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F19,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G19,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H19,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I19,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J19,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K19,$A$11:$A$94,0)),0))</f>
+        <v>46334</v>
       </c>
       <c r="M19" s="18">
         <f>IF(E19=0,IF(COUNTA(F19:K19)=0,$D$2,L19),WORKDAY.INTL(L19,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46349</v>
+        <v>46335</v>
       </c>
       <c r="N19" s="18">
         <f>IF(E19=0,M19,WORKDAY.INTL(M19,E19-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46376</v>
+        <v>46341</v>
       </c>
       <c r="O19" s="19"/>
       <c r="P19" s="15" t="s">
@@ -2712,124 +2769,74 @@
       </c>
     </row>
     <row r="20" spans="1:87">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="14"/>
-      <c r="AE20" s="14"/>
-      <c r="AF20" s="14"/>
-      <c r="AG20" s="14"/>
-      <c r="AH20" s="14"/>
-      <c r="AI20" s="14"/>
-      <c r="AJ20" s="14"/>
-      <c r="AK20" s="14"/>
-      <c r="AL20" s="14"/>
-      <c r="AM20" s="14"/>
-      <c r="AN20" s="14"/>
-      <c r="AO20" s="14"/>
-      <c r="AP20" s="14"/>
-      <c r="AQ20" s="14"/>
-      <c r="AR20" s="14"/>
-      <c r="AS20" s="14"/>
-      <c r="AT20" s="14"/>
-      <c r="AU20" s="14"/>
-      <c r="AV20" s="14"/>
-      <c r="AW20" s="14"/>
-      <c r="AX20" s="14"/>
-      <c r="AY20" s="14"/>
-      <c r="AZ20" s="14"/>
-      <c r="BA20" s="14"/>
-      <c r="BB20" s="14"/>
-      <c r="BC20" s="14"/>
-      <c r="BD20" s="14"/>
-      <c r="BE20" s="14"/>
-      <c r="BF20" s="14"/>
-      <c r="BG20" s="14"/>
-      <c r="BH20" s="14"/>
-      <c r="BI20" s="14"/>
-      <c r="BJ20" s="14"/>
-      <c r="BK20" s="14"/>
-      <c r="BL20" s="14"/>
-      <c r="BM20" s="14"/>
-      <c r="BN20" s="14"/>
-      <c r="BO20" s="14"/>
-      <c r="BP20" s="14"/>
-      <c r="BQ20" s="14"/>
-      <c r="BR20" s="14"/>
-      <c r="BS20" s="14"/>
-      <c r="BT20" s="14"/>
-      <c r="BU20" s="14"/>
-      <c r="BV20" s="14"/>
-      <c r="BW20" s="14"/>
-      <c r="BX20" s="14"/>
-      <c r="BY20" s="14"/>
-      <c r="BZ20" s="14"/>
-      <c r="CA20" s="14"/>
-      <c r="CB20" s="14"/>
-      <c r="CC20" s="14"/>
-      <c r="CD20" s="14"/>
-      <c r="CE20" s="14"/>
-      <c r="CF20" s="14"/>
-      <c r="CG20" s="14"/>
-      <c r="CH20" s="14"/>
-      <c r="CI20" s="14"/>
+      <c r="B20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="17">
+        <v>20</v>
+      </c>
+      <c r="E20" s="15">
+        <f>D20</f>
+        <v>20</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F20,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G20,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H20,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I20,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J20,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K20,$A$11:$A$94,0)),0))</f>
+        <v>46348</v>
+      </c>
+      <c r="M20" s="18">
+        <f>IF(E20=0,IF(COUNTA(F20:K20)=0,$D$2,L20),WORKDAY.INTL(L20,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46349</v>
+      </c>
+      <c r="N20" s="18">
+        <f>IF(E20=0,M20,WORKDAY.INTL(M20,E20-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46376</v>
+      </c>
+      <c r="O20" s="19"/>
+      <c r="P20" s="15" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" spans="1:87">
       <c r="A21" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D21" s="17">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E21" s="15">
-        <f>IF(D21=0,0,MAX(1,ROUNDUP(D21/$D$5,0)))</f>
-        <v>5</v>
+        <f>D21</f>
+        <v>20</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>76</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="G21" s="15"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
       <c r="L21" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J21,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K21,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F21,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G21,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H21,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I21,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J21,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K21,$A$11:$A$94,0)),0))</f>
         <v>46348</v>
       </c>
       <c r="M21" s="18">
@@ -2838,60 +2845,104 @@
       </c>
       <c r="N21" s="18">
         <f>IF(E21=0,M21,WORKDAY.INTL(M21,E21-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46355</v>
-      </c>
-      <c r="O21" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46376</v>
+      </c>
+      <c r="O21" s="19"/>
       <c r="P21" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:87">
-      <c r="A22" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="17">
-        <v>4</v>
-      </c>
-      <c r="E22" s="15">
-        <f>IF(D22=0,0,MAX(1,ROUNDUP(D22/$D$5,0)))</f>
-        <v>4</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J22,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K22,$A$11:$A$86,0)),0))</f>
-        <v>46355</v>
-      </c>
-      <c r="M22" s="18">
-        <f>IF(E22=0,IF(COUNTA(F22:K22)=0,$D$2,L22),WORKDAY.INTL(L22,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46356</v>
-      </c>
-      <c r="N22" s="18">
-        <f>IF(E22=0,M22,WORKDAY.INTL(M22,E22-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46359</v>
-      </c>
-      <c r="O22" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="P22" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:87">
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
+      <c r="AE22" s="14"/>
+      <c r="AF22" s="14"/>
+      <c r="AG22" s="14"/>
+      <c r="AH22" s="14"/>
+      <c r="AI22" s="14"/>
+      <c r="AJ22" s="14"/>
+      <c r="AK22" s="14"/>
+      <c r="AL22" s="14"/>
+      <c r="AM22" s="14"/>
+      <c r="AN22" s="14"/>
+      <c r="AO22" s="14"/>
+      <c r="AP22" s="14"/>
+      <c r="AQ22" s="14"/>
+      <c r="AR22" s="14"/>
+      <c r="AS22" s="14"/>
+      <c r="AT22" s="14"/>
+      <c r="AU22" s="14"/>
+      <c r="AV22" s="14"/>
+      <c r="AW22" s="14"/>
+      <c r="AX22" s="14"/>
+      <c r="AY22" s="14"/>
+      <c r="AZ22" s="14"/>
+      <c r="BA22" s="14"/>
+      <c r="BB22" s="14"/>
+      <c r="BC22" s="14"/>
+      <c r="BD22" s="14"/>
+      <c r="BE22" s="14"/>
+      <c r="BF22" s="14"/>
+      <c r="BG22" s="14"/>
+      <c r="BH22" s="14"/>
+      <c r="BI22" s="14"/>
+      <c r="BJ22" s="14"/>
+      <c r="BK22" s="14"/>
+      <c r="BL22" s="14"/>
+      <c r="BM22" s="14"/>
+      <c r="BN22" s="14"/>
+      <c r="BO22" s="14"/>
+      <c r="BP22" s="14"/>
+      <c r="BQ22" s="14"/>
+      <c r="BR22" s="14"/>
+      <c r="BS22" s="14"/>
+      <c r="BT22" s="14"/>
+      <c r="BU22" s="14"/>
+      <c r="BV22" s="14"/>
+      <c r="BW22" s="14"/>
+      <c r="BX22" s="14"/>
+      <c r="BY22" s="14"/>
+      <c r="BZ22" s="14"/>
+      <c r="CA22" s="14"/>
+      <c r="CB22" s="14"/>
+      <c r="CC22" s="14"/>
+      <c r="CD22" s="14"/>
+      <c r="CE22" s="14"/>
+      <c r="CF22" s="14"/>
+      <c r="CG22" s="14"/>
+      <c r="CH22" s="14"/>
+      <c r="CI22" s="14"/>
+    </row>
+    <row r="23" spans="1:87" ht="26" customHeight="1">
       <c r="A23" s="15" t="s">
         <v>98</v>
       </c>
@@ -2899,34 +2950,38 @@
         <v>99</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D23" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <f>D23</f>
-        <v>1</v>
+        <f>IF(D23=0,0,MAX(1,ROUNDUP(D23/$D$5,0)))</f>
+        <v>5</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
+        <v>74</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>70</v>
+      </c>
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
       <c r="L23" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J23,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K23,$A$11:$A$86,0)),0))</f>
-        <v>46359</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F23,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G23,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H23,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I23,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J23,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K23,$A$11:$A$94,0)),0))</f>
+        <v>46348</v>
       </c>
       <c r="M23" s="18">
         <f>IF(E23=0,IF(COUNTA(F23:K23)=0,$D$2,L23),WORKDAY.INTL(L23,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46362</v>
+        <v>46349</v>
       </c>
       <c r="N23" s="18">
         <f>IF(E23=0,M23,WORKDAY.INTL(M23,E23-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46362</v>
+        <v>46355</v>
       </c>
       <c r="O23" s="19" t="s">
         <v>68</v>
@@ -2936,114 +2991,68 @@
       </c>
     </row>
     <row r="24" spans="1:87">
-      <c r="A24" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
-      <c r="AD24" s="14"/>
-      <c r="AE24" s="14"/>
-      <c r="AF24" s="14"/>
-      <c r="AG24" s="14"/>
-      <c r="AH24" s="14"/>
-      <c r="AI24" s="14"/>
-      <c r="AJ24" s="14"/>
-      <c r="AK24" s="14"/>
-      <c r="AL24" s="14"/>
-      <c r="AM24" s="14"/>
-      <c r="AN24" s="14"/>
-      <c r="AO24" s="14"/>
-      <c r="AP24" s="14"/>
-      <c r="AQ24" s="14"/>
-      <c r="AR24" s="14"/>
-      <c r="AS24" s="14"/>
-      <c r="AT24" s="14"/>
-      <c r="AU24" s="14"/>
-      <c r="AV24" s="14"/>
-      <c r="AW24" s="14"/>
-      <c r="AX24" s="14"/>
-      <c r="AY24" s="14"/>
-      <c r="AZ24" s="14"/>
-      <c r="BA24" s="14"/>
-      <c r="BB24" s="14"/>
-      <c r="BC24" s="14"/>
-      <c r="BD24" s="14"/>
-      <c r="BE24" s="14"/>
-      <c r="BF24" s="14"/>
-      <c r="BG24" s="14"/>
-      <c r="BH24" s="14"/>
-      <c r="BI24" s="14"/>
-      <c r="BJ24" s="14"/>
-      <c r="BK24" s="14"/>
-      <c r="BL24" s="14"/>
-      <c r="BM24" s="14"/>
-      <c r="BN24" s="14"/>
-      <c r="BO24" s="14"/>
-      <c r="BP24" s="14"/>
-      <c r="BQ24" s="14"/>
-      <c r="BR24" s="14"/>
-      <c r="BS24" s="14"/>
-      <c r="BT24" s="14"/>
-      <c r="BU24" s="14"/>
-      <c r="BV24" s="14"/>
-      <c r="BW24" s="14"/>
-      <c r="BX24" s="14"/>
-      <c r="BY24" s="14"/>
-      <c r="BZ24" s="14"/>
-      <c r="CA24" s="14"/>
-      <c r="CB24" s="14"/>
-      <c r="CC24" s="14"/>
-      <c r="CD24" s="14"/>
-      <c r="CE24" s="14"/>
-      <c r="CF24" s="14"/>
-      <c r="CG24" s="14"/>
-      <c r="CH24" s="14"/>
-      <c r="CI24" s="14"/>
+      <c r="A24" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="17">
+        <v>4</v>
+      </c>
+      <c r="E24" s="15">
+        <f>IF(D24=0,0,MAX(1,ROUNDUP(D24/$D$5,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F24,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G24,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H24,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I24,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J24,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K24,$A$11:$A$94,0)),0))</f>
+        <v>46355</v>
+      </c>
+      <c r="M24" s="18">
+        <f>IF(E24=0,IF(COUNTA(F24:K24)=0,$D$2,L24),WORKDAY.INTL(L24,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46356</v>
+      </c>
+      <c r="N24" s="18">
+        <f>IF(E24=0,M24,WORKDAY.INTL(M24,E24-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46359</v>
+      </c>
+      <c r="O24" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="P24" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="25" spans="1:87" ht="26" customHeight="1">
       <c r="A25" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="17">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15">
+        <f>D25</f>
+        <v>1</v>
+      </c>
+      <c r="F25" s="15" t="s">
         <v>101</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="17">
-        <v>8</v>
-      </c>
-      <c r="E25" s="15">
-        <f>IF(D25=0,0,MAX(1,ROUNDUP(D25/$D$5,0)))</f>
-        <v>7</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>98</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
@@ -3051,16 +3060,16 @@
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
       <c r="L25" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J25,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K25,$A$11:$A$86,0)),0))</f>
-        <v>46362</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F25,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G25,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H25,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I25,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J25,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K25,$A$11:$A$94,0)),0))</f>
+        <v>46359</v>
       </c>
       <c r="M25" s="18">
         <f>IF(E25=0,IF(COUNTA(F25:K25)=0,$D$2,L25),WORKDAY.INTL(L25,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46363</v>
+        <v>46362</v>
       </c>
       <c r="N25" s="18">
         <f>IF(E25=0,M25,WORKDAY.INTL(M25,E25-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46371</v>
+        <v>46362</v>
       </c>
       <c r="O25" s="19" t="s">
         <v>68</v>
@@ -3070,48 +3079,96 @@
       </c>
     </row>
     <row r="26" spans="1:87">
-      <c r="A26" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="17">
-        <v>3</v>
-      </c>
-      <c r="E26" s="15">
-        <f>IF(D26=0,0,MAX(1,ROUNDUP(D26/$D$5,0)))</f>
-        <v>3</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J26,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K26,$A$11:$A$86,0)),0))</f>
-        <v>46371</v>
-      </c>
-      <c r="M26" s="18">
-        <f>IF(E26=0,IF(COUNTA(F26:K26)=0,$D$2,L26),WORKDAY.INTL(L26,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46372</v>
-      </c>
-      <c r="N26" s="18">
-        <f>IF(E26=0,M26,WORKDAY.INTL(M26,E26-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46376</v>
-      </c>
-      <c r="O26" s="19"/>
-      <c r="P26" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:87">
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+      <c r="AE26" s="14"/>
+      <c r="AF26" s="14"/>
+      <c r="AG26" s="14"/>
+      <c r="AH26" s="14"/>
+      <c r="AI26" s="14"/>
+      <c r="AJ26" s="14"/>
+      <c r="AK26" s="14"/>
+      <c r="AL26" s="14"/>
+      <c r="AM26" s="14"/>
+      <c r="AN26" s="14"/>
+      <c r="AO26" s="14"/>
+      <c r="AP26" s="14"/>
+      <c r="AQ26" s="14"/>
+      <c r="AR26" s="14"/>
+      <c r="AS26" s="14"/>
+      <c r="AT26" s="14"/>
+      <c r="AU26" s="14"/>
+      <c r="AV26" s="14"/>
+      <c r="AW26" s="14"/>
+      <c r="AX26" s="14"/>
+      <c r="AY26" s="14"/>
+      <c r="AZ26" s="14"/>
+      <c r="BA26" s="14"/>
+      <c r="BB26" s="14"/>
+      <c r="BC26" s="14"/>
+      <c r="BD26" s="14"/>
+      <c r="BE26" s="14"/>
+      <c r="BF26" s="14"/>
+      <c r="BG26" s="14"/>
+      <c r="BH26" s="14"/>
+      <c r="BI26" s="14"/>
+      <c r="BJ26" s="14"/>
+      <c r="BK26" s="14"/>
+      <c r="BL26" s="14"/>
+      <c r="BM26" s="14"/>
+      <c r="BN26" s="14"/>
+      <c r="BO26" s="14"/>
+      <c r="BP26" s="14"/>
+      <c r="BQ26" s="14"/>
+      <c r="BR26" s="14"/>
+      <c r="BS26" s="14"/>
+      <c r="BT26" s="14"/>
+      <c r="BU26" s="14"/>
+      <c r="BV26" s="14"/>
+      <c r="BW26" s="14"/>
+      <c r="BX26" s="14"/>
+      <c r="BY26" s="14"/>
+      <c r="BZ26" s="14"/>
+      <c r="CA26" s="14"/>
+      <c r="CB26" s="14"/>
+      <c r="CC26" s="14"/>
+      <c r="CD26" s="14"/>
+      <c r="CE26" s="14"/>
+      <c r="CF26" s="14"/>
+      <c r="CG26" s="14"/>
+      <c r="CH26" s="14"/>
+      <c r="CI26" s="14"/>
+    </row>
+    <row r="27" spans="1:87" ht="26" customHeight="1">
       <c r="A27" s="15" t="s">
         <v>107</v>
       </c>
@@ -3122,14 +3179,14 @@
         <v>109</v>
       </c>
       <c r="D27" s="17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E27" s="15">
         <f>IF(D27=0,0,MAX(1,ROUNDUP(D27/$D$5,0)))</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
@@ -3137,18 +3194,20 @@
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
       <c r="L27" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J27,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K27,$A$11:$A$86,0)),0))</f>
-        <v>46371</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F27,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G27,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H27,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I27,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J27,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K27,$A$11:$A$94,0)),0))</f>
+        <v>46362</v>
       </c>
       <c r="M27" s="18">
         <f>IF(E27=0,IF(COUNTA(F27:K27)=0,$D$2,L27),WORKDAY.INTL(L27,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46372</v>
+        <v>46363</v>
       </c>
       <c r="N27" s="18">
         <f>IF(E27=0,M27,WORKDAY.INTL(M27,E27-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46376</v>
-      </c>
-      <c r="O27" s="19"/>
+        <v>46371</v>
+      </c>
+      <c r="O27" s="19" t="s">
+        <v>68</v>
+      </c>
       <c r="P27" s="15" t="s">
         <v>69</v>
       </c>
@@ -3164,14 +3223,14 @@
         <v>112</v>
       </c>
       <c r="D28" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <f>IF(D28=0,0,MAX(1,ROUNDUP(D28/$D$5,0)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
@@ -3179,7 +3238,7 @@
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
       <c r="L28" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J28,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K28,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F28,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G28,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H28,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I28,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J28,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K28,$A$11:$A$94,0)),0))</f>
         <v>46371</v>
       </c>
       <c r="M28" s="18">
@@ -3188,7 +3247,7 @@
       </c>
       <c r="N28" s="18">
         <f>IF(E28=0,M28,WORKDAY.INTL(M28,E28-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46377</v>
+        <v>46376</v>
       </c>
       <c r="O28" s="19"/>
       <c r="P28" s="15" t="s">
@@ -3206,14 +3265,14 @@
         <v>115</v>
       </c>
       <c r="D29" s="17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" s="15">
         <f>IF(D29=0,0,MAX(1,ROUNDUP(D29/$D$5,0)))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
@@ -3221,7 +3280,7 @@
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
       <c r="L29" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J29,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K29,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F29,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G29,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H29,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I29,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J29,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K29,$A$11:$A$94,0)),0))</f>
         <v>46371</v>
       </c>
       <c r="M29" s="18">
@@ -3230,11 +3289,9 @@
       </c>
       <c r="N29" s="18">
         <f>IF(E29=0,M29,WORKDAY.INTL(M29,E29-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46379</v>
-      </c>
-      <c r="O29" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46376</v>
+      </c>
+      <c r="O29" s="19"/>
       <c r="P29" s="15" t="s">
         <v>69</v>
       </c>
@@ -3250,33 +3307,31 @@
         <v>118</v>
       </c>
       <c r="D30" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" s="15">
         <f>IF(D30=0,0,MAX(1,ROUNDUP(D30/$D$5,0)))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>76</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="G30" s="15"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
       <c r="L30" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J30,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K30,$A$11:$A$86,0)),0))</f>
-        <v>46362</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F30,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G30,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H30,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I30,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J30,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K30,$A$11:$A$94,0)),0))</f>
+        <v>46371</v>
       </c>
       <c r="M30" s="18">
         <f>IF(E30=0,IF(COUNTA(F30:K30)=0,$D$2,L30),WORKDAY.INTL(L30,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46363</v>
+        <v>46372</v>
       </c>
       <c r="N30" s="18">
         <f>IF(E30=0,M30,WORKDAY.INTL(M30,E30-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46369</v>
+        <v>46377</v>
       </c>
       <c r="O30" s="19"/>
       <c r="P30" s="15" t="s">
@@ -3291,17 +3346,17 @@
         <v>120</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D31" s="17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E31" s="15">
-        <f>D31</f>
-        <v>1</v>
+        <f>IF(D31=0,0,MAX(1,ROUNDUP(D31/$D$5,0)))</f>
+        <v>6</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15"/>
@@ -3309,89 +3364,87 @@
       <c r="J31" s="15"/>
       <c r="K31" s="15"/>
       <c r="L31" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J31,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K31,$A$11:$A$86,0)),0))</f>
-        <v>46369</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F31,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G31,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H31,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I31,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J31,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K31,$A$11:$A$94,0)),0))</f>
+        <v>46371</v>
       </c>
       <c r="M31" s="18">
         <f>IF(E31=0,IF(COUNTA(F31:K31)=0,$D$2,L31),WORKDAY.INTL(L31,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46370</v>
+        <v>46372</v>
       </c>
       <c r="N31" s="18">
         <f>IF(E31=0,M31,WORKDAY.INTL(M31,E31-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46370</v>
-      </c>
-      <c r="O31" s="19"/>
+        <v>46379</v>
+      </c>
+      <c r="O31" s="19" t="s">
+        <v>68</v>
+      </c>
       <c r="P31" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:87" ht="26" customHeight="1">
+    <row r="32" spans="1:87">
       <c r="A32" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="15">
         <f>IF(D32=0,0,MAX(1,ROUNDUP(D32/$D$5,0)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>70</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="H32" s="15"/>
       <c r="I32" s="15"/>
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
       <c r="L32" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J32,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K32,$A$11:$A$86,0)),0))</f>
-        <v>46371</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F32,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G32,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H32,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I32,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J32,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K32,$A$11:$A$94,0)),0))</f>
+        <v>46362</v>
       </c>
       <c r="M32" s="18">
         <f>IF(E32=0,IF(COUNTA(F32:K32)=0,$D$2,L32),WORKDAY.INTL(L32,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46372</v>
+        <v>46363</v>
       </c>
       <c r="N32" s="18">
         <f>IF(E32=0,M32,WORKDAY.INTL(M32,E32-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46379</v>
-      </c>
-      <c r="O32" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46369</v>
+      </c>
+      <c r="O32" s="19"/>
       <c r="P32" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:87">
       <c r="A33" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>126</v>
-      </c>
       <c r="D33" s="17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E33" s="15">
-        <f>IF(D33=0,0,MAX(1,ROUNDUP(D33/$D$5,0)))</f>
-        <v>6</v>
+        <f>D33</f>
+        <v>1</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15"/>
@@ -3399,12 +3452,12 @@
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
       <c r="L33" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J33,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K33,$A$11:$A$86,0)),0))</f>
-        <v>46362</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F33,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G33,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H33,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I33,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J33,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K33,$A$11:$A$94,0)),0))</f>
+        <v>46369</v>
       </c>
       <c r="M33" s="18">
         <f>IF(E33=0,IF(COUNTA(F33:K33)=0,$D$2,L33),WORKDAY.INTL(L33,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46363</v>
+        <v>46370</v>
       </c>
       <c r="N33" s="18">
         <f>IF(E33=0,M33,WORKDAY.INTL(M33,E33-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
@@ -3415,7 +3468,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:87">
+    <row r="34" spans="1:87" ht="26" customHeight="1">
       <c r="A34" s="15" t="s">
         <v>127</v>
       </c>
@@ -3426,41 +3479,35 @@
         <v>129</v>
       </c>
       <c r="D34" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E34" s="15">
         <f>IF(D34=0,0,MAX(1,ROUNDUP(D34/$D$5,0)))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G34" s="15" t="s">
         <v>107</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="J34" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>124</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
       <c r="L34" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J34,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K34,$A$11:$A$86,0)),0))</f>
-        <v>46379</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F34,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G34,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H34,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I34,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J34,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K34,$A$11:$A$94,0)),0))</f>
+        <v>46371</v>
       </c>
       <c r="M34" s="18">
         <f>IF(E34=0,IF(COUNTA(F34:K34)=0,$D$2,L34),WORKDAY.INTL(L34,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46380</v>
+        <v>46372</v>
       </c>
       <c r="N34" s="18">
         <f>IF(E34=0,M34,WORKDAY.INTL(M34,E34-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46385</v>
+        <v>46379</v>
       </c>
       <c r="O34" s="19" t="s">
         <v>68</v>
@@ -3477,17 +3524,17 @@
         <v>131</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="D35" s="17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E35" s="15">
-        <f>D35</f>
-        <v>2</v>
+        <f>IF(D35=0,0,MAX(1,ROUNDUP(D35/$D$5,0)))</f>
+        <v>6</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="G35" s="15"/>
       <c r="H35" s="15"/>
@@ -3495,133 +3542,95 @@
       <c r="J35" s="15"/>
       <c r="K35" s="15"/>
       <c r="L35" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J35,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K35,$A$11:$A$86,0)),0))</f>
-        <v>46385</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F35,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G35,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H35,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I35,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J35,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K35,$A$11:$A$94,0)),0))</f>
+        <v>46362</v>
       </c>
       <c r="M35" s="18">
         <f>IF(E35=0,IF(COUNTA(F35:K35)=0,$D$2,L35),WORKDAY.INTL(L35,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46386</v>
+        <v>46363</v>
       </c>
       <c r="N35" s="18">
         <f>IF(E35=0,M35,WORKDAY.INTL(M35,E35-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46387</v>
-      </c>
-      <c r="O35" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46370</v>
+      </c>
+      <c r="O35" s="19"/>
       <c r="P35" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:87">
-      <c r="A36" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
-      <c r="X36" s="14"/>
-      <c r="Y36" s="14"/>
-      <c r="Z36" s="14"/>
-      <c r="AA36" s="14"/>
-      <c r="AB36" s="14"/>
-      <c r="AC36" s="14"/>
-      <c r="AD36" s="14"/>
-      <c r="AE36" s="14"/>
-      <c r="AF36" s="14"/>
-      <c r="AG36" s="14"/>
-      <c r="AH36" s="14"/>
-      <c r="AI36" s="14"/>
-      <c r="AJ36" s="14"/>
-      <c r="AK36" s="14"/>
-      <c r="AL36" s="14"/>
-      <c r="AM36" s="14"/>
-      <c r="AN36" s="14"/>
-      <c r="AO36" s="14"/>
-      <c r="AP36" s="14"/>
-      <c r="AQ36" s="14"/>
-      <c r="AR36" s="14"/>
-      <c r="AS36" s="14"/>
-      <c r="AT36" s="14"/>
-      <c r="AU36" s="14"/>
-      <c r="AV36" s="14"/>
-      <c r="AW36" s="14"/>
-      <c r="AX36" s="14"/>
-      <c r="AY36" s="14"/>
-      <c r="AZ36" s="14"/>
-      <c r="BA36" s="14"/>
-      <c r="BB36" s="14"/>
-      <c r="BC36" s="14"/>
-      <c r="BD36" s="14"/>
-      <c r="BE36" s="14"/>
-      <c r="BF36" s="14"/>
-      <c r="BG36" s="14"/>
-      <c r="BH36" s="14"/>
-      <c r="BI36" s="14"/>
-      <c r="BJ36" s="14"/>
-      <c r="BK36" s="14"/>
-      <c r="BL36" s="14"/>
-      <c r="BM36" s="14"/>
-      <c r="BN36" s="14"/>
-      <c r="BO36" s="14"/>
-      <c r="BP36" s="14"/>
-      <c r="BQ36" s="14"/>
-      <c r="BR36" s="14"/>
-      <c r="BS36" s="14"/>
-      <c r="BT36" s="14"/>
-      <c r="BU36" s="14"/>
-      <c r="BV36" s="14"/>
-      <c r="BW36" s="14"/>
-      <c r="BX36" s="14"/>
-      <c r="BY36" s="14"/>
-      <c r="BZ36" s="14"/>
-      <c r="CA36" s="14"/>
-      <c r="CB36" s="14"/>
-      <c r="CC36" s="14"/>
-      <c r="CD36" s="14"/>
-      <c r="CE36" s="14"/>
-      <c r="CF36" s="14"/>
-      <c r="CG36" s="14"/>
-      <c r="CH36" s="14"/>
-      <c r="CI36" s="14"/>
+      <c r="A36" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D36" s="17">
+        <v>4</v>
+      </c>
+      <c r="E36" s="15">
+        <f>IF(D36=0,0,MAX(1,ROUNDUP(D36/$D$5,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L36" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F36,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G36,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H36,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I36,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J36,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K36,$A$11:$A$94,0)),0))</f>
+        <v>46379</v>
+      </c>
+      <c r="M36" s="18">
+        <f>IF(E36=0,IF(COUNTA(F36:K36)=0,$D$2,L36),WORKDAY.INTL(L36,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46380</v>
+      </c>
+      <c r="N36" s="18">
+        <f>IF(E36=0,M36,WORKDAY.INTL(M36,E36-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46385</v>
+      </c>
+      <c r="O36" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="P36" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" spans="1:87">
       <c r="A37" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="17">
+        <v>2</v>
+      </c>
+      <c r="E37" s="15">
+        <f>D37</f>
+        <v>2</v>
+      </c>
+      <c r="F37" s="15" t="s">
         <v>133</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D37" s="17">
-        <v>10</v>
-      </c>
-      <c r="E37" s="15">
-        <f>IF(D37=0,0,MAX(1,ROUNDUP(D37/$D$5,0)))</f>
-        <v>9</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>130</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="15"/>
@@ -3629,65 +3638,113 @@
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
       <c r="L37" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J37,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K37,$A$11:$A$86,0)),0))</f>
-        <v>46387</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F37,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G37,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H37,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I37,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J37,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K37,$A$11:$A$94,0)),0))</f>
+        <v>46385</v>
       </c>
       <c r="M37" s="18">
         <f>IF(E37=0,IF(COUNTA(F37:K37)=0,$D$2,L37),WORKDAY.INTL(L37,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46390</v>
+        <v>46386</v>
       </c>
       <c r="N37" s="18">
         <f>IF(E37=0,M37,WORKDAY.INTL(M37,E37-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46400</v>
-      </c>
-      <c r="O37" s="19"/>
+        <v>46387</v>
+      </c>
+      <c r="O37" s="19" t="s">
+        <v>68</v>
+      </c>
       <c r="P37" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:87">
-      <c r="A38" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="16" t="s">
+      <c r="A38" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="17">
-        <v>15</v>
-      </c>
-      <c r="E38" s="15">
-        <f>IF(D38=0,0,MAX(1,ROUNDUP(D38/$D$5,0)))</f>
-        <v>13</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J38,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K38,$A$11:$A$86,0)),0))</f>
-        <v>46387</v>
-      </c>
-      <c r="M38" s="18">
-        <f>IF(E38=0,IF(COUNTA(F38:K38)=0,$D$2,L38),WORKDAY.INTL(L38,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46390</v>
-      </c>
-      <c r="N38" s="18">
-        <f>IF(E38=0,M38,WORKDAY.INTL(M38,E38-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46406</v>
-      </c>
-      <c r="O38" s="19"/>
-      <c r="P38" s="15" t="s">
-        <v>69</v>
-      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="14"/>
+      <c r="T38" s="14"/>
+      <c r="U38" s="14"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="14"/>
+      <c r="Z38" s="14"/>
+      <c r="AA38" s="14"/>
+      <c r="AB38" s="14"/>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="14"/>
+      <c r="AE38" s="14"/>
+      <c r="AF38" s="14"/>
+      <c r="AG38" s="14"/>
+      <c r="AH38" s="14"/>
+      <c r="AI38" s="14"/>
+      <c r="AJ38" s="14"/>
+      <c r="AK38" s="14"/>
+      <c r="AL38" s="14"/>
+      <c r="AM38" s="14"/>
+      <c r="AN38" s="14"/>
+      <c r="AO38" s="14"/>
+      <c r="AP38" s="14"/>
+      <c r="AQ38" s="14"/>
+      <c r="AR38" s="14"/>
+      <c r="AS38" s="14"/>
+      <c r="AT38" s="14"/>
+      <c r="AU38" s="14"/>
+      <c r="AV38" s="14"/>
+      <c r="AW38" s="14"/>
+      <c r="AX38" s="14"/>
+      <c r="AY38" s="14"/>
+      <c r="AZ38" s="14"/>
+      <c r="BA38" s="14"/>
+      <c r="BB38" s="14"/>
+      <c r="BC38" s="14"/>
+      <c r="BD38" s="14"/>
+      <c r="BE38" s="14"/>
+      <c r="BF38" s="14"/>
+      <c r="BG38" s="14"/>
+      <c r="BH38" s="14"/>
+      <c r="BI38" s="14"/>
+      <c r="BJ38" s="14"/>
+      <c r="BK38" s="14"/>
+      <c r="BL38" s="14"/>
+      <c r="BM38" s="14"/>
+      <c r="BN38" s="14"/>
+      <c r="BO38" s="14"/>
+      <c r="BP38" s="14"/>
+      <c r="BQ38" s="14"/>
+      <c r="BR38" s="14"/>
+      <c r="BS38" s="14"/>
+      <c r="BT38" s="14"/>
+      <c r="BU38" s="14"/>
+      <c r="BV38" s="14"/>
+      <c r="BW38" s="14"/>
+      <c r="BX38" s="14"/>
+      <c r="BY38" s="14"/>
+      <c r="BZ38" s="14"/>
+      <c r="CA38" s="14"/>
+      <c r="CB38" s="14"/>
+      <c r="CC38" s="14"/>
+      <c r="CD38" s="14"/>
+      <c r="CE38" s="14"/>
+      <c r="CF38" s="14"/>
+      <c r="CG38" s="14"/>
+      <c r="CH38" s="14"/>
+      <c r="CI38" s="14"/>
     </row>
     <row r="39" spans="1:87">
       <c r="A39" s="15" t="s">
@@ -3700,11 +3757,11 @@
         <v>141</v>
       </c>
       <c r="D39" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E39" s="15">
         <f>IF(D39=0,0,MAX(1,ROUNDUP(D39/$D$5,0)))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>136</v>
@@ -3715,16 +3772,16 @@
       <c r="J39" s="15"/>
       <c r="K39" s="15"/>
       <c r="L39" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J39,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K39,$A$11:$A$86,0)),0))</f>
-        <v>46406</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F39,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G39,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H39,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I39,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J39,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K39,$A$11:$A$94,0)),0))</f>
+        <v>46387</v>
       </c>
       <c r="M39" s="18">
         <f>IF(E39=0,IF(COUNTA(F39:K39)=0,$D$2,L39),WORKDAY.INTL(L39,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46407</v>
+        <v>46390</v>
       </c>
       <c r="N39" s="18">
         <f>IF(E39=0,M39,WORKDAY.INTL(M39,E39-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46415</v>
+        <v>46400</v>
       </c>
       <c r="O39" s="19"/>
       <c r="P39" s="15" t="s">
@@ -3742,14 +3799,14 @@
         <v>144</v>
       </c>
       <c r="D40" s="17">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E40" s="15">
         <f>IF(D40=0,0,MAX(1,ROUNDUP(D40/$D$5,0)))</f>
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G40" s="15" t="s">
         <v>70</v>
@@ -3759,7 +3816,7 @@
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
       <c r="L40" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J40,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K40,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F40,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G40,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H40,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I40,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J40,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K40,$A$11:$A$94,0)),0))</f>
         <v>46387</v>
       </c>
       <c r="M40" s="18">
@@ -3768,7 +3825,7 @@
       </c>
       <c r="N40" s="18">
         <f>IF(E40=0,M40,WORKDAY.INTL(M40,E40-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46421</v>
+        <v>46406</v>
       </c>
       <c r="O40" s="19"/>
       <c r="P40" s="15" t="s">
@@ -3786,37 +3843,33 @@
         <v>147</v>
       </c>
       <c r="D41" s="17">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E41" s="15">
         <f>IF(D41=0,0,MAX(1,ROUNDUP(D41/$D$5,0)))</f>
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>70</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G41" s="15"/>
       <c r="H41" s="15"/>
       <c r="I41" s="15"/>
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
       <c r="L41" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J41,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K41,$A$11:$A$86,0)),0))</f>
-        <v>46387</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F41,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G41,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H41,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I41,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J41,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K41,$A$11:$A$94,0)),0))</f>
+        <v>46406</v>
       </c>
       <c r="M41" s="18">
         <f>IF(E41=0,IF(COUNTA(F41:K41)=0,$D$2,L41),WORKDAY.INTL(L41,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46390</v>
+        <v>46407</v>
       </c>
       <c r="N41" s="18">
         <f>IF(E41=0,M41,WORKDAY.INTL(M41,E41-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46429</v>
-      </c>
-      <c r="O41" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46415</v>
+      </c>
+      <c r="O41" s="19"/>
       <c r="P41" s="15" t="s">
         <v>69</v>
       </c>
@@ -3829,167 +3882,113 @@
         <v>149</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D42" s="17">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E42" s="15">
-        <f>D42</f>
-        <v>2</v>
+        <f>IF(D42=0,0,MAX(1,ROUNDUP(D42/$D$5,0)))</f>
+        <v>24</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>145</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
       <c r="K42" s="15"/>
       <c r="L42" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J42,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K42,$A$11:$A$86,0)),0))</f>
-        <v>46429</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F42,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G42,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H42,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I42,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J42,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K42,$A$11:$A$94,0)),0))</f>
+        <v>46387</v>
       </c>
       <c r="M42" s="18">
         <f>IF(E42=0,IF(COUNTA(F42:K42)=0,$D$2,L42),WORKDAY.INTL(L42,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46432</v>
+        <v>46390</v>
       </c>
       <c r="N42" s="18">
         <f>IF(E42=0,M42,WORKDAY.INTL(M42,E42-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46433</v>
-      </c>
-      <c r="O42" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46421</v>
+      </c>
+      <c r="O42" s="19"/>
       <c r="P42" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:87">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
-      <c r="R43" s="14"/>
-      <c r="S43" s="14"/>
-      <c r="T43" s="14"/>
-      <c r="U43" s="14"/>
-      <c r="V43" s="14"/>
-      <c r="W43" s="14"/>
-      <c r="X43" s="14"/>
-      <c r="Y43" s="14"/>
-      <c r="Z43" s="14"/>
-      <c r="AA43" s="14"/>
-      <c r="AB43" s="14"/>
-      <c r="AC43" s="14"/>
-      <c r="AD43" s="14"/>
-      <c r="AE43" s="14"/>
-      <c r="AF43" s="14"/>
-      <c r="AG43" s="14"/>
-      <c r="AH43" s="14"/>
-      <c r="AI43" s="14"/>
-      <c r="AJ43" s="14"/>
-      <c r="AK43" s="14"/>
-      <c r="AL43" s="14"/>
-      <c r="AM43" s="14"/>
-      <c r="AN43" s="14"/>
-      <c r="AO43" s="14"/>
-      <c r="AP43" s="14"/>
-      <c r="AQ43" s="14"/>
-      <c r="AR43" s="14"/>
-      <c r="AS43" s="14"/>
-      <c r="AT43" s="14"/>
-      <c r="AU43" s="14"/>
-      <c r="AV43" s="14"/>
-      <c r="AW43" s="14"/>
-      <c r="AX43" s="14"/>
-      <c r="AY43" s="14"/>
-      <c r="AZ43" s="14"/>
-      <c r="BA43" s="14"/>
-      <c r="BB43" s="14"/>
-      <c r="BC43" s="14"/>
-      <c r="BD43" s="14"/>
-      <c r="BE43" s="14"/>
-      <c r="BF43" s="14"/>
-      <c r="BG43" s="14"/>
-      <c r="BH43" s="14"/>
-      <c r="BI43" s="14"/>
-      <c r="BJ43" s="14"/>
-      <c r="BK43" s="14"/>
-      <c r="BL43" s="14"/>
-      <c r="BM43" s="14"/>
-      <c r="BN43" s="14"/>
-      <c r="BO43" s="14"/>
-      <c r="BP43" s="14"/>
-      <c r="BQ43" s="14"/>
-      <c r="BR43" s="14"/>
-      <c r="BS43" s="14"/>
-      <c r="BT43" s="14"/>
-      <c r="BU43" s="14"/>
-      <c r="BV43" s="14"/>
-      <c r="BW43" s="14"/>
-      <c r="BX43" s="14"/>
-      <c r="BY43" s="14"/>
-      <c r="BZ43" s="14"/>
-      <c r="CA43" s="14"/>
-      <c r="CB43" s="14"/>
-      <c r="CC43" s="14"/>
-      <c r="CD43" s="14"/>
-      <c r="CE43" s="14"/>
-      <c r="CF43" s="14"/>
-      <c r="CG43" s="14"/>
-      <c r="CH43" s="14"/>
-      <c r="CI43" s="14"/>
+      <c r="D43" s="17">
+        <v>2</v>
+      </c>
+      <c r="E43" s="15">
+        <f>IF(D43=0,0,MAX(1,ROUNDUP(D43/$D$5,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F43,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G43,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H43,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I43,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J43,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K43,$A$11:$A$94,0)),0))</f>
+        <v>46421</v>
+      </c>
+      <c r="M43" s="18">
+        <f>IF(E43=0,IF(COUNTA(F43:K43)=0,$D$2,L43),WORKDAY.INTL(L43,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46422</v>
+      </c>
+      <c r="N43" s="18">
+        <f>IF(E43=0,M43,WORKDAY.INTL(M43,E43-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46425</v>
+      </c>
+      <c r="O43" s="19"/>
+      <c r="P43" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="44" spans="1:87">
       <c r="A44" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D44" s="17">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E44" s="15">
         <f>IF(D44=0,0,MAX(1,ROUNDUP(D44/$D$5,0)))</f>
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G44" s="15"/>
+        <v>136</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>70</v>
+      </c>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
       <c r="J44" s="15"/>
       <c r="K44" s="15"/>
       <c r="L44" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J44,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K44,$A$11:$A$86,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F44,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G44,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H44,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I44,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J44,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K44,$A$11:$A$94,0)),0))</f>
         <v>46387</v>
       </c>
       <c r="M44" s="18">
@@ -3998,7 +3997,7 @@
       </c>
       <c r="N44" s="18">
         <f>IF(E44=0,M44,WORKDAY.INTL(M44,E44-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46393</v>
+        <v>46429</v>
       </c>
       <c r="O44" s="19"/>
       <c r="P44" s="15" t="s">
@@ -4007,42 +4006,50 @@
     </row>
     <row r="45" spans="1:87">
       <c r="A45" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="D45" s="17">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E45" s="15">
-        <f>IF(D45=0,0,MAX(1,ROUNDUP(D45/$D$5,0)))</f>
-        <v>17</v>
+        <f>D45</f>
+        <v>2</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G45" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="J45" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
+      <c r="K45" s="15" t="s">
+        <v>153</v>
+      </c>
       <c r="L45" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J45,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K45,$A$11:$A$86,0)),0))</f>
-        <v>46393</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F45,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G45,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H45,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I45,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J45,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K45,$A$11:$A$94,0)),0))</f>
+        <v>46429</v>
       </c>
       <c r="M45" s="18">
         <f>IF(E45=0,IF(COUNTA(F45:K45)=0,$D$2,L45),WORKDAY.INTL(L45,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46394</v>
+        <v>46432</v>
       </c>
       <c r="N45" s="18">
         <f>IF(E45=0,M45,WORKDAY.INTL(M45,E45-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46418</v>
+        <v>46433</v>
       </c>
       <c r="O45" s="19"/>
       <c r="P45" s="15" t="s">
@@ -4050,68 +4057,114 @@
       </c>
     </row>
     <row r="46" spans="1:87">
-      <c r="A46" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B46" s="16" t="s">
+      <c r="A46" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C46" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D46" s="17">
-        <v>20</v>
-      </c>
-      <c r="E46" s="15">
-        <f>IF(D46=0,0,MAX(1,ROUNDUP(D46/$D$5,0)))</f>
-        <v>17</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G46" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J46,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K46,$A$11:$A$86,0)),0))</f>
-        <v>46393</v>
-      </c>
-      <c r="M46" s="18">
-        <f>IF(E46=0,IF(COUNTA(F46:K46)=0,$D$2,L46),WORKDAY.INTL(L46,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46394</v>
-      </c>
-      <c r="N46" s="18">
-        <f>IF(E46=0,M46,WORKDAY.INTL(M46,E46-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46418</v>
-      </c>
-      <c r="O46" s="19"/>
-      <c r="P46" s="15" t="s">
-        <v>69</v>
-      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="13"/>
+      <c r="R46" s="14"/>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
+      <c r="Y46" s="14"/>
+      <c r="Z46" s="14"/>
+      <c r="AA46" s="14"/>
+      <c r="AB46" s="14"/>
+      <c r="AC46" s="14"/>
+      <c r="AD46" s="14"/>
+      <c r="AE46" s="14"/>
+      <c r="AF46" s="14"/>
+      <c r="AG46" s="14"/>
+      <c r="AH46" s="14"/>
+      <c r="AI46" s="14"/>
+      <c r="AJ46" s="14"/>
+      <c r="AK46" s="14"/>
+      <c r="AL46" s="14"/>
+      <c r="AM46" s="14"/>
+      <c r="AN46" s="14"/>
+      <c r="AO46" s="14"/>
+      <c r="AP46" s="14"/>
+      <c r="AQ46" s="14"/>
+      <c r="AR46" s="14"/>
+      <c r="AS46" s="14"/>
+      <c r="AT46" s="14"/>
+      <c r="AU46" s="14"/>
+      <c r="AV46" s="14"/>
+      <c r="AW46" s="14"/>
+      <c r="AX46" s="14"/>
+      <c r="AY46" s="14"/>
+      <c r="AZ46" s="14"/>
+      <c r="BA46" s="14"/>
+      <c r="BB46" s="14"/>
+      <c r="BC46" s="14"/>
+      <c r="BD46" s="14"/>
+      <c r="BE46" s="14"/>
+      <c r="BF46" s="14"/>
+      <c r="BG46" s="14"/>
+      <c r="BH46" s="14"/>
+      <c r="BI46" s="14"/>
+      <c r="BJ46" s="14"/>
+      <c r="BK46" s="14"/>
+      <c r="BL46" s="14"/>
+      <c r="BM46" s="14"/>
+      <c r="BN46" s="14"/>
+      <c r="BO46" s="14"/>
+      <c r="BP46" s="14"/>
+      <c r="BQ46" s="14"/>
+      <c r="BR46" s="14"/>
+      <c r="BS46" s="14"/>
+      <c r="BT46" s="14"/>
+      <c r="BU46" s="14"/>
+      <c r="BV46" s="14"/>
+      <c r="BW46" s="14"/>
+      <c r="BX46" s="14"/>
+      <c r="BY46" s="14"/>
+      <c r="BZ46" s="14"/>
+      <c r="CA46" s="14"/>
+      <c r="CB46" s="14"/>
+      <c r="CC46" s="14"/>
+      <c r="CD46" s="14"/>
+      <c r="CE46" s="14"/>
+      <c r="CF46" s="14"/>
+      <c r="CG46" s="14"/>
+      <c r="CH46" s="14"/>
+      <c r="CI46" s="14"/>
     </row>
     <row r="47" spans="1:87">
       <c r="A47" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B47" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="C47" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>162</v>
-      </c>
       <c r="D47" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" s="15">
-        <f>D47</f>
-        <v>3</v>
+        <f>IF(D47=0,0,MAX(1,ROUNDUP(D47/$D$5,0)))</f>
+        <v>4</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" s="15"/>
@@ -4119,16 +4172,16 @@
       <c r="J47" s="15"/>
       <c r="K47" s="15"/>
       <c r="L47" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J47,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K47,$A$11:$A$86,0)),0))</f>
-        <v>46418</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F47,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G47,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H47,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I47,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J47,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K47,$A$11:$A$94,0)),0))</f>
+        <v>46387</v>
       </c>
       <c r="M47" s="18">
         <f>IF(E47=0,IF(COUNTA(F47:K47)=0,$D$2,L47),WORKDAY.INTL(L47,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46419</v>
+        <v>46390</v>
       </c>
       <c r="N47" s="18">
         <f>IF(E47=0,M47,WORKDAY.INTL(M47,E47-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46421</v>
+        <v>46393</v>
       </c>
       <c r="O47" s="19"/>
       <c r="P47" s="15" t="s">
@@ -4137,40 +4190,42 @@
     </row>
     <row r="48" spans="1:87">
       <c r="A48" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="C48" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="C48" s="16" t="s">
-        <v>165</v>
-      </c>
       <c r="D48" s="17">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E48" s="15">
-        <f>D48</f>
-        <v>3</v>
+        <f>IF(D48=0,0,MAX(1,ROUNDUP(D48/$D$5,0)))</f>
+        <v>17</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="G48" s="15"/>
+        <v>136</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>159</v>
+      </c>
       <c r="H48" s="15"/>
       <c r="I48" s="15"/>
       <c r="J48" s="15"/>
       <c r="K48" s="15"/>
       <c r="L48" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J48,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K48,$A$11:$A$86,0)),0))</f>
-        <v>46418</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F48,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G48,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H48,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I48,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J48,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K48,$A$11:$A$94,0)),0))</f>
+        <v>46393</v>
       </c>
       <c r="M48" s="18">
         <f>IF(E48=0,IF(COUNTA(F48:K48)=0,$D$2,L48),WORKDAY.INTL(L48,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46419</v>
+        <v>46394</v>
       </c>
       <c r="N48" s="18">
         <f>IF(E48=0,M48,WORKDAY.INTL(M48,E48-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46421</v>
+        <v>46418</v>
       </c>
       <c r="O48" s="19"/>
       <c r="P48" s="15" t="s">
@@ -4178,162 +4233,114 @@
       </c>
     </row>
     <row r="49" spans="1:87">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B49" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="R49" s="14"/>
-      <c r="S49" s="14"/>
-      <c r="T49" s="14"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="14"/>
-      <c r="W49" s="14"/>
-      <c r="X49" s="14"/>
-      <c r="Y49" s="14"/>
-      <c r="Z49" s="14"/>
-      <c r="AA49" s="14"/>
-      <c r="AB49" s="14"/>
-      <c r="AC49" s="14"/>
-      <c r="AD49" s="14"/>
-      <c r="AE49" s="14"/>
-      <c r="AF49" s="14"/>
-      <c r="AG49" s="14"/>
-      <c r="AH49" s="14"/>
-      <c r="AI49" s="14"/>
-      <c r="AJ49" s="14"/>
-      <c r="AK49" s="14"/>
-      <c r="AL49" s="14"/>
-      <c r="AM49" s="14"/>
-      <c r="AN49" s="14"/>
-      <c r="AO49" s="14"/>
-      <c r="AP49" s="14"/>
-      <c r="AQ49" s="14"/>
-      <c r="AR49" s="14"/>
-      <c r="AS49" s="14"/>
-      <c r="AT49" s="14"/>
-      <c r="AU49" s="14"/>
-      <c r="AV49" s="14"/>
-      <c r="AW49" s="14"/>
-      <c r="AX49" s="14"/>
-      <c r="AY49" s="14"/>
-      <c r="AZ49" s="14"/>
-      <c r="BA49" s="14"/>
-      <c r="BB49" s="14"/>
-      <c r="BC49" s="14"/>
-      <c r="BD49" s="14"/>
-      <c r="BE49" s="14"/>
-      <c r="BF49" s="14"/>
-      <c r="BG49" s="14"/>
-      <c r="BH49" s="14"/>
-      <c r="BI49" s="14"/>
-      <c r="BJ49" s="14"/>
-      <c r="BK49" s="14"/>
-      <c r="BL49" s="14"/>
-      <c r="BM49" s="14"/>
-      <c r="BN49" s="14"/>
-      <c r="BO49" s="14"/>
-      <c r="BP49" s="14"/>
-      <c r="BQ49" s="14"/>
-      <c r="BR49" s="14"/>
-      <c r="BS49" s="14"/>
-      <c r="BT49" s="14"/>
-      <c r="BU49" s="14"/>
-      <c r="BV49" s="14"/>
-      <c r="BW49" s="14"/>
-      <c r="BX49" s="14"/>
-      <c r="BY49" s="14"/>
-      <c r="BZ49" s="14"/>
-      <c r="CA49" s="14"/>
-      <c r="CB49" s="14"/>
-      <c r="CC49" s="14"/>
-      <c r="CD49" s="14"/>
-      <c r="CE49" s="14"/>
-      <c r="CF49" s="14"/>
-      <c r="CG49" s="14"/>
-      <c r="CH49" s="14"/>
-      <c r="CI49" s="14"/>
-    </row>
-    <row r="50" spans="1:87">
+      <c r="C49" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" s="17">
+        <v>20</v>
+      </c>
+      <c r="E49" s="15">
+        <f>IF(D49=0,0,MAX(1,ROUNDUP(D49/$D$5,0)))</f>
+        <v>17</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F49,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G49,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H49,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I49,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J49,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K49,$A$11:$A$94,0)),0))</f>
+        <v>46393</v>
+      </c>
+      <c r="M49" s="18">
+        <f>IF(E49=0,IF(COUNTA(F49:K49)=0,$D$2,L49),WORKDAY.INTL(L49,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46394</v>
+      </c>
+      <c r="N49" s="18">
+        <f>IF(E49=0,M49,WORKDAY.INTL(M49,E49-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46418</v>
+      </c>
+      <c r="O49" s="19"/>
+      <c r="P49" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:87" ht="26" customHeight="1">
       <c r="A50" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D50" s="17">
         <v>12</v>
       </c>
       <c r="E50" s="15">
-        <f>IF(D50=0,0,MAX(1,ROUNDUP(D50/$D$5,0)))</f>
-        <v>11</v>
+        <f>D50</f>
+        <v>12</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>148</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="H50" s="15"/>
       <c r="I50" s="15"/>
       <c r="J50" s="15"/>
       <c r="K50" s="15"/>
       <c r="L50" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J50,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K50,$A$11:$A$86,0)),0))</f>
-        <v>46433</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F50,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G50,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H50,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I50,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J50,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K50,$A$11:$A$94,0)),0))</f>
+        <v>46393</v>
       </c>
       <c r="M50" s="18">
         <f>IF(E50=0,IF(COUNTA(F50:K50)=0,$D$2,L50),WORKDAY.INTL(L50,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46434</v>
+        <v>46394</v>
       </c>
       <c r="N50" s="18">
         <f>IF(E50=0,M50,WORKDAY.INTL(M50,E50-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46448</v>
-      </c>
-      <c r="O50" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46411</v>
+      </c>
+      <c r="O50" s="19"/>
       <c r="P50" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:87">
       <c r="A51" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D51" s="17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E51" s="15">
-        <f>IF(D51=0,0,MAX(1,ROUNDUP(D51/$D$5,0)))</f>
-        <v>6</v>
+        <f>D51</f>
+        <v>3</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15"/>
@@ -4341,43 +4348,41 @@
       <c r="J51" s="15"/>
       <c r="K51" s="15"/>
       <c r="L51" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J51,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K51,$A$11:$A$86,0)),0))</f>
-        <v>46448</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F51,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G51,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H51,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I51,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J51,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K51,$A$11:$A$94,0)),0))</f>
+        <v>46418</v>
       </c>
       <c r="M51" s="18">
         <f>IF(E51=0,IF(COUNTA(F51:K51)=0,$D$2,L51),WORKDAY.INTL(L51,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46449</v>
+        <v>46419</v>
       </c>
       <c r="N51" s="18">
         <f>IF(E51=0,M51,WORKDAY.INTL(M51,E51-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46456</v>
-      </c>
-      <c r="O51" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46421</v>
+      </c>
+      <c r="O51" s="19"/>
       <c r="P51" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:87">
       <c r="A52" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="D52" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="15">
         <f>D52</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G52" s="15"/>
       <c r="H52" s="15"/>
@@ -4385,67 +4390,111 @@
       <c r="J52" s="15"/>
       <c r="K52" s="15"/>
       <c r="L52" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J52,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K52,$A$11:$A$86,0)),0))</f>
-        <v>46456</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F52,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G52,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H52,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I52,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J52,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K52,$A$11:$A$94,0)),0))</f>
+        <v>46418</v>
       </c>
       <c r="M52" s="18">
         <f>IF(E52=0,IF(COUNTA(F52:K52)=0,$D$2,L52),WORKDAY.INTL(L52,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46457</v>
+        <v>46419</v>
       </c>
       <c r="N52" s="18">
         <f>IF(E52=0,M52,WORKDAY.INTL(M52,E52-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46460</v>
-      </c>
-      <c r="O52" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46421</v>
+      </c>
+      <c r="O52" s="19"/>
       <c r="P52" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:87">
-      <c r="A53" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="C53" s="16" t="s">
+      <c r="A53" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="D53" s="17">
-        <v>6</v>
-      </c>
-      <c r="E53" s="15">
-        <f>IF(D53=0,0,MAX(1,ROUNDUP(D53/$D$5,0)))</f>
-        <v>6</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="G53" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J53,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K53,$A$11:$A$86,0)),0))</f>
-        <v>46421</v>
-      </c>
-      <c r="M53" s="18">
-        <f>IF(E53=0,IF(COUNTA(F53:K53)=0,$D$2,L53),WORKDAY.INTL(L53,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46422</v>
-      </c>
-      <c r="N53" s="18">
-        <f>IF(E53=0,M53,WORKDAY.INTL(M53,E53-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46429</v>
-      </c>
-      <c r="O53" s="19"/>
-      <c r="P53" s="15" t="s">
-        <v>69</v>
-      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="13"/>
+      <c r="R53" s="14"/>
+      <c r="S53" s="14"/>
+      <c r="T53" s="14"/>
+      <c r="U53" s="14"/>
+      <c r="V53" s="14"/>
+      <c r="W53" s="14"/>
+      <c r="X53" s="14"/>
+      <c r="Y53" s="14"/>
+      <c r="Z53" s="14"/>
+      <c r="AA53" s="14"/>
+      <c r="AB53" s="14"/>
+      <c r="AC53" s="14"/>
+      <c r="AD53" s="14"/>
+      <c r="AE53" s="14"/>
+      <c r="AF53" s="14"/>
+      <c r="AG53" s="14"/>
+      <c r="AH53" s="14"/>
+      <c r="AI53" s="14"/>
+      <c r="AJ53" s="14"/>
+      <c r="AK53" s="14"/>
+      <c r="AL53" s="14"/>
+      <c r="AM53" s="14"/>
+      <c r="AN53" s="14"/>
+      <c r="AO53" s="14"/>
+      <c r="AP53" s="14"/>
+      <c r="AQ53" s="14"/>
+      <c r="AR53" s="14"/>
+      <c r="AS53" s="14"/>
+      <c r="AT53" s="14"/>
+      <c r="AU53" s="14"/>
+      <c r="AV53" s="14"/>
+      <c r="AW53" s="14"/>
+      <c r="AX53" s="14"/>
+      <c r="AY53" s="14"/>
+      <c r="AZ53" s="14"/>
+      <c r="BA53" s="14"/>
+      <c r="BB53" s="14"/>
+      <c r="BC53" s="14"/>
+      <c r="BD53" s="14"/>
+      <c r="BE53" s="14"/>
+      <c r="BF53" s="14"/>
+      <c r="BG53" s="14"/>
+      <c r="BH53" s="14"/>
+      <c r="BI53" s="14"/>
+      <c r="BJ53" s="14"/>
+      <c r="BK53" s="14"/>
+      <c r="BL53" s="14"/>
+      <c r="BM53" s="14"/>
+      <c r="BN53" s="14"/>
+      <c r="BO53" s="14"/>
+      <c r="BP53" s="14"/>
+      <c r="BQ53" s="14"/>
+      <c r="BR53" s="14"/>
+      <c r="BS53" s="14"/>
+      <c r="BT53" s="14"/>
+      <c r="BU53" s="14"/>
+      <c r="BV53" s="14"/>
+      <c r="BW53" s="14"/>
+      <c r="BX53" s="14"/>
+      <c r="BY53" s="14"/>
+      <c r="BZ53" s="14"/>
+      <c r="CA53" s="14"/>
+      <c r="CB53" s="14"/>
+      <c r="CC53" s="14"/>
+      <c r="CD53" s="14"/>
+      <c r="CE53" s="14"/>
+      <c r="CF53" s="14"/>
+      <c r="CG53" s="14"/>
+      <c r="CH53" s="14"/>
+      <c r="CI53" s="14"/>
     </row>
     <row r="54" spans="1:87">
       <c r="A54" s="15" t="s">
@@ -4458,33 +4507,37 @@
         <v>180</v>
       </c>
       <c r="D54" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E54" s="15">
         <f>IF(D54=0,0,MAX(1,ROUNDUP(D54/$D$5,0)))</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
+        <v>174</v>
+      </c>
+      <c r="H54" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>168</v>
+      </c>
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
       <c r="L54" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J54,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K54,$A$11:$A$86,0)),0))</f>
-        <v>46421</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F54,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G54,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H54,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I54,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J54,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K54,$A$11:$A$94,0)),0))</f>
+        <v>46433</v>
       </c>
       <c r="M54" s="18">
         <f>IF(E54=0,IF(COUNTA(F54:K54)=0,$D$2,L54),WORKDAY.INTL(L54,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46422</v>
+        <v>46434</v>
       </c>
       <c r="N54" s="18">
         <f>IF(E54=0,M54,WORKDAY.INTL(M54,E54-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46429</v>
+        <v>46448</v>
       </c>
       <c r="O54" s="19"/>
       <c r="P54" s="15" t="s">
@@ -4502,33 +4555,31 @@
         <v>183</v>
       </c>
       <c r="D55" s="17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E55" s="15">
-        <f>D55</f>
-        <v>3</v>
+        <f>IF(D55=0,0,MAX(1,ROUNDUP(D55/$D$5,0)))</f>
+        <v>6</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="G55" s="15" t="s">
         <v>178</v>
       </c>
+      <c r="G55" s="15"/>
       <c r="H55" s="15"/>
       <c r="I55" s="15"/>
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
       <c r="L55" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J55,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K55,$A$11:$A$86,0)),0))</f>
-        <v>46429</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F55,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G55,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H55,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I55,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J55,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K55,$A$11:$A$94,0)),0))</f>
+        <v>46448</v>
       </c>
       <c r="M55" s="18">
         <f>IF(E55=0,IF(COUNTA(F55:K55)=0,$D$2,L55),WORKDAY.INTL(L55,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46432</v>
+        <v>46449</v>
       </c>
       <c r="N55" s="18">
         <f>IF(E55=0,M55,WORKDAY.INTL(M55,E55-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46434</v>
+        <v>46456</v>
       </c>
       <c r="O55" s="19"/>
       <c r="P55" s="15" t="s">
@@ -4546,11 +4597,11 @@
         <v>67</v>
       </c>
       <c r="D56" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="15">
         <f>D56</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>181</v>
@@ -4561,16 +4612,16 @@
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
       <c r="L56" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J56,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K56,$A$11:$A$86,0)),0))</f>
-        <v>46434</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F56,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G56,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H56,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I56,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J56,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K56,$A$11:$A$94,0)),0))</f>
+        <v>46456</v>
       </c>
       <c r="M56" s="18">
         <f>IF(E56=0,IF(COUNTA(F56:K56)=0,$D$2,L56),WORKDAY.INTL(L56,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46435</v>
+        <v>46457</v>
       </c>
       <c r="N56" s="18">
         <f>IF(E56=0,M56,WORKDAY.INTL(M56,E56-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46435</v>
+        <v>46460</v>
       </c>
       <c r="O56" s="19"/>
       <c r="P56" s="15" t="s">
@@ -4578,177 +4629,135 @@
       </c>
     </row>
     <row r="57" spans="1:87">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
-      <c r="L57" s="13"/>
-      <c r="M57" s="13"/>
-      <c r="N57" s="13"/>
-      <c r="O57" s="13"/>
-      <c r="P57" s="13"/>
-      <c r="R57" s="14"/>
-      <c r="S57" s="14"/>
-      <c r="T57" s="14"/>
-      <c r="U57" s="14"/>
-      <c r="V57" s="14"/>
-      <c r="W57" s="14"/>
-      <c r="X57" s="14"/>
-      <c r="Y57" s="14"/>
-      <c r="Z57" s="14"/>
-      <c r="AA57" s="14"/>
-      <c r="AB57" s="14"/>
-      <c r="AC57" s="14"/>
-      <c r="AD57" s="14"/>
-      <c r="AE57" s="14"/>
-      <c r="AF57" s="14"/>
-      <c r="AG57" s="14"/>
-      <c r="AH57" s="14"/>
-      <c r="AI57" s="14"/>
-      <c r="AJ57" s="14"/>
-      <c r="AK57" s="14"/>
-      <c r="AL57" s="14"/>
-      <c r="AM57" s="14"/>
-      <c r="AN57" s="14"/>
-      <c r="AO57" s="14"/>
-      <c r="AP57" s="14"/>
-      <c r="AQ57" s="14"/>
-      <c r="AR57" s="14"/>
-      <c r="AS57" s="14"/>
-      <c r="AT57" s="14"/>
-      <c r="AU57" s="14"/>
-      <c r="AV57" s="14"/>
-      <c r="AW57" s="14"/>
-      <c r="AX57" s="14"/>
-      <c r="AY57" s="14"/>
-      <c r="AZ57" s="14"/>
-      <c r="BA57" s="14"/>
-      <c r="BB57" s="14"/>
-      <c r="BC57" s="14"/>
-      <c r="BD57" s="14"/>
-      <c r="BE57" s="14"/>
-      <c r="BF57" s="14"/>
-      <c r="BG57" s="14"/>
-      <c r="BH57" s="14"/>
-      <c r="BI57" s="14"/>
-      <c r="BJ57" s="14"/>
-      <c r="BK57" s="14"/>
-      <c r="BL57" s="14"/>
-      <c r="BM57" s="14"/>
-      <c r="BN57" s="14"/>
-      <c r="BO57" s="14"/>
-      <c r="BP57" s="14"/>
-      <c r="BQ57" s="14"/>
-      <c r="BR57" s="14"/>
-      <c r="BS57" s="14"/>
-      <c r="BT57" s="14"/>
-      <c r="BU57" s="14"/>
-      <c r="BV57" s="14"/>
-      <c r="BW57" s="14"/>
-      <c r="BX57" s="14"/>
-      <c r="BY57" s="14"/>
-      <c r="BZ57" s="14"/>
-      <c r="CA57" s="14"/>
-      <c r="CB57" s="14"/>
-      <c r="CC57" s="14"/>
-      <c r="CD57" s="14"/>
-      <c r="CE57" s="14"/>
-      <c r="CF57" s="14"/>
-      <c r="CG57" s="14"/>
-      <c r="CH57" s="14"/>
-      <c r="CI57" s="14"/>
+      <c r="B57" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D57" s="17">
+        <v>6</v>
+      </c>
+      <c r="E57" s="15">
+        <f>IF(D57=0,0,MAX(1,ROUNDUP(D57/$D$5,0)))</f>
+        <v>6</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F57,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G57,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H57,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I57,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J57,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K57,$A$11:$A$94,0)),0))</f>
+        <v>46421</v>
+      </c>
+      <c r="M57" s="18">
+        <f>IF(E57=0,IF(COUNTA(F57:K57)=0,$D$2,L57),WORKDAY.INTL(L57,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46422</v>
+      </c>
+      <c r="N57" s="18">
+        <f>IF(E57=0,M57,WORKDAY.INTL(M57,E57-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46429</v>
+      </c>
+      <c r="O57" s="19"/>
+      <c r="P57" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="58" spans="1:87">
       <c r="A58" s="15" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D58" s="17">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E58" s="15">
-        <f>D58</f>
-        <v>40</v>
+        <f>IF(D58=0,0,MAX(1,ROUNDUP(D58/$D$5,0)))</f>
+        <v>6</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
+        <v>148</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="I58" s="15"/>
       <c r="J58" s="15"/>
       <c r="K58" s="15"/>
       <c r="L58" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J58,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K58,$A$11:$A$86,0)),0))</f>
-        <v>46387</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F58,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G58,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H58,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I58,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J58,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K58,$A$11:$A$94,0)),0))</f>
+        <v>46421</v>
       </c>
       <c r="M58" s="18">
         <f>IF(E58=0,IF(COUNTA(F58:K58)=0,$D$2,L58),WORKDAY.INTL(L58,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46390</v>
+        <v>46422</v>
       </c>
       <c r="N58" s="18">
         <f>IF(E58=0,M58,WORKDAY.INTL(M58,E58-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46443</v>
+        <v>46429</v>
       </c>
       <c r="O58" s="19"/>
       <c r="P58" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:87">
       <c r="A59" s="15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="D59" s="17">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E59" s="15">
-        <f>IF(D59=0,0,MAX(1,ROUNDUP(D59/$D$5,0)))</f>
-        <v>17</v>
+        <f>D59</f>
+        <v>3</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="H59" s="15" t="s">
-        <v>121</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="H59" s="15"/>
       <c r="I59" s="15"/>
       <c r="J59" s="15"/>
       <c r="K59" s="15"/>
       <c r="L59" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J59,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K59,$A$11:$A$86,0)),0))</f>
-        <v>46443</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F59,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G59,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H59,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I59,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J59,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K59,$A$11:$A$94,0)),0))</f>
+        <v>46429</v>
       </c>
       <c r="M59" s="18">
         <f>IF(E59=0,IF(COUNTA(F59:K59)=0,$D$2,L59),WORKDAY.INTL(L59,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46446</v>
+        <v>46432</v>
       </c>
       <c r="N59" s="18">
         <f>IF(E59=0,M59,WORKDAY.INTL(M59,E59-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46468</v>
+        <v>46434</v>
       </c>
       <c r="O59" s="19"/>
       <c r="P59" s="15" t="s">
@@ -4757,42 +4766,40 @@
     </row>
     <row r="60" spans="1:87">
       <c r="A60" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="17">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15">
+        <f>D60</f>
+        <v>1</v>
+      </c>
+      <c r="F60" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="D60" s="17">
-        <v>8</v>
-      </c>
-      <c r="E60" s="15">
-        <f>IF(D60=0,0,MAX(1,ROUNDUP(D60/$D$5,0)))</f>
-        <v>7</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="G60" s="15" t="s">
-        <v>190</v>
-      </c>
+      <c r="G60" s="15"/>
       <c r="H60" s="15"/>
       <c r="I60" s="15"/>
       <c r="J60" s="15"/>
       <c r="K60" s="15"/>
       <c r="L60" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J60,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K60,$A$11:$A$86,0)),0))</f>
-        <v>46468</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F60,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G60,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H60,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I60,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J60,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K60,$A$11:$A$94,0)),0))</f>
+        <v>46434</v>
       </c>
       <c r="M60" s="18">
         <f>IF(E60=0,IF(COUNTA(F60:K60)=0,$D$2,L60),WORKDAY.INTL(L60,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46469</v>
+        <v>46435</v>
       </c>
       <c r="N60" s="18">
         <f>IF(E60=0,M60,WORKDAY.INTL(M60,E60-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46477</v>
+        <v>46435</v>
       </c>
       <c r="O60" s="19"/>
       <c r="P60" s="15" t="s">
@@ -4800,229 +4807,225 @@
       </c>
     </row>
     <row r="61" spans="1:87">
-      <c r="A61" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61" s="17">
-        <v>4</v>
-      </c>
-      <c r="E61" s="15">
-        <f>IF(D61=0,0,MAX(1,ROUNDUP(D61/$D$5,0)))</f>
-        <v>4</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="G61" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J61,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K61,$A$11:$A$86,0)),0))</f>
-        <v>46477</v>
-      </c>
-      <c r="M61" s="18">
-        <f>IF(E61=0,IF(COUNTA(F61:K61)=0,$D$2,L61),WORKDAY.INTL(L61,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46478</v>
-      </c>
-      <c r="N61" s="18">
-        <f>IF(E61=0,M61,WORKDAY.INTL(M61,E61-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46483</v>
-      </c>
-      <c r="O61" s="19"/>
-      <c r="P61" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="62" spans="1:87">
-      <c r="A62" s="13" t="s">
+      <c r="A61" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
-      <c r="L62" s="13"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
-      <c r="R62" s="14"/>
-      <c r="S62" s="14"/>
-      <c r="T62" s="14"/>
-      <c r="U62" s="14"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="14"/>
-      <c r="X62" s="14"/>
-      <c r="Y62" s="14"/>
-      <c r="Z62" s="14"/>
-      <c r="AA62" s="14"/>
-      <c r="AB62" s="14"/>
-      <c r="AC62" s="14"/>
-      <c r="AD62" s="14"/>
-      <c r="AE62" s="14"/>
-      <c r="AF62" s="14"/>
-      <c r="AG62" s="14"/>
-      <c r="AH62" s="14"/>
-      <c r="AI62" s="14"/>
-      <c r="AJ62" s="14"/>
-      <c r="AK62" s="14"/>
-      <c r="AL62" s="14"/>
-      <c r="AM62" s="14"/>
-      <c r="AN62" s="14"/>
-      <c r="AO62" s="14"/>
-      <c r="AP62" s="14"/>
-      <c r="AQ62" s="14"/>
-      <c r="AR62" s="14"/>
-      <c r="AS62" s="14"/>
-      <c r="AT62" s="14"/>
-      <c r="AU62" s="14"/>
-      <c r="AV62" s="14"/>
-      <c r="AW62" s="14"/>
-      <c r="AX62" s="14"/>
-      <c r="AY62" s="14"/>
-      <c r="AZ62" s="14"/>
-      <c r="BA62" s="14"/>
-      <c r="BB62" s="14"/>
-      <c r="BC62" s="14"/>
-      <c r="BD62" s="14"/>
-      <c r="BE62" s="14"/>
-      <c r="BF62" s="14"/>
-      <c r="BG62" s="14"/>
-      <c r="BH62" s="14"/>
-      <c r="BI62" s="14"/>
-      <c r="BJ62" s="14"/>
-      <c r="BK62" s="14"/>
-      <c r="BL62" s="14"/>
-      <c r="BM62" s="14"/>
-      <c r="BN62" s="14"/>
-      <c r="BO62" s="14"/>
-      <c r="BP62" s="14"/>
-      <c r="BQ62" s="14"/>
-      <c r="BR62" s="14"/>
-      <c r="BS62" s="14"/>
-      <c r="BT62" s="14"/>
-      <c r="BU62" s="14"/>
-      <c r="BV62" s="14"/>
-      <c r="BW62" s="14"/>
-      <c r="BX62" s="14"/>
-      <c r="BY62" s="14"/>
-      <c r="BZ62" s="14"/>
-      <c r="CA62" s="14"/>
-      <c r="CB62" s="14"/>
-      <c r="CC62" s="14"/>
-      <c r="CD62" s="14"/>
-      <c r="CE62" s="14"/>
-      <c r="CF62" s="14"/>
-      <c r="CG62" s="14"/>
-      <c r="CH62" s="14"/>
-      <c r="CI62" s="14"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13"/>
+      <c r="P61" s="13"/>
+      <c r="R61" s="14"/>
+      <c r="S61" s="14"/>
+      <c r="T61" s="14"/>
+      <c r="U61" s="14"/>
+      <c r="V61" s="14"/>
+      <c r="W61" s="14"/>
+      <c r="X61" s="14"/>
+      <c r="Y61" s="14"/>
+      <c r="Z61" s="14"/>
+      <c r="AA61" s="14"/>
+      <c r="AB61" s="14"/>
+      <c r="AC61" s="14"/>
+      <c r="AD61" s="14"/>
+      <c r="AE61" s="14"/>
+      <c r="AF61" s="14"/>
+      <c r="AG61" s="14"/>
+      <c r="AH61" s="14"/>
+      <c r="AI61" s="14"/>
+      <c r="AJ61" s="14"/>
+      <c r="AK61" s="14"/>
+      <c r="AL61" s="14"/>
+      <c r="AM61" s="14"/>
+      <c r="AN61" s="14"/>
+      <c r="AO61" s="14"/>
+      <c r="AP61" s="14"/>
+      <c r="AQ61" s="14"/>
+      <c r="AR61" s="14"/>
+      <c r="AS61" s="14"/>
+      <c r="AT61" s="14"/>
+      <c r="AU61" s="14"/>
+      <c r="AV61" s="14"/>
+      <c r="AW61" s="14"/>
+      <c r="AX61" s="14"/>
+      <c r="AY61" s="14"/>
+      <c r="AZ61" s="14"/>
+      <c r="BA61" s="14"/>
+      <c r="BB61" s="14"/>
+      <c r="BC61" s="14"/>
+      <c r="BD61" s="14"/>
+      <c r="BE61" s="14"/>
+      <c r="BF61" s="14"/>
+      <c r="BG61" s="14"/>
+      <c r="BH61" s="14"/>
+      <c r="BI61" s="14"/>
+      <c r="BJ61" s="14"/>
+      <c r="BK61" s="14"/>
+      <c r="BL61" s="14"/>
+      <c r="BM61" s="14"/>
+      <c r="BN61" s="14"/>
+      <c r="BO61" s="14"/>
+      <c r="BP61" s="14"/>
+      <c r="BQ61" s="14"/>
+      <c r="BR61" s="14"/>
+      <c r="BS61" s="14"/>
+      <c r="BT61" s="14"/>
+      <c r="BU61" s="14"/>
+      <c r="BV61" s="14"/>
+      <c r="BW61" s="14"/>
+      <c r="BX61" s="14"/>
+      <c r="BY61" s="14"/>
+      <c r="BZ61" s="14"/>
+      <c r="CA61" s="14"/>
+      <c r="CB61" s="14"/>
+      <c r="CC61" s="14"/>
+      <c r="CD61" s="14"/>
+      <c r="CE61" s="14"/>
+      <c r="CF61" s="14"/>
+      <c r="CG61" s="14"/>
+      <c r="CH61" s="14"/>
+      <c r="CI61" s="14"/>
+    </row>
+    <row r="62" spans="1:87" ht="26" customHeight="1">
+      <c r="A62" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D62" s="17">
+        <v>25</v>
+      </c>
+      <c r="E62" s="15">
+        <f>D62</f>
+        <v>25</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G62" s="15"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F62,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G62,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H62,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I62,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J62,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K62,$A$11:$A$94,0)),0))</f>
+        <v>46387</v>
+      </c>
+      <c r="M62" s="18">
+        <f>IF(E62=0,IF(COUNTA(F62:K62)=0,$D$2,L62),WORKDAY.INTL(L62,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46390</v>
+      </c>
+      <c r="N62" s="18">
+        <f>IF(E62=0,M62,WORKDAY.INTL(M62,E62-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46422</v>
+      </c>
+      <c r="O62" s="19"/>
+      <c r="P62" s="15" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="63" spans="1:87">
       <c r="A63" s="15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="D63" s="17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E63" s="15">
         <f>IF(D63=0,0,MAX(1,ROUNDUP(D63/$D$5,0)))</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="H63" s="15"/>
+        <v>198</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>127</v>
+      </c>
       <c r="I63" s="15"/>
       <c r="J63" s="15"/>
       <c r="K63" s="15"/>
       <c r="L63" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J63,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K63,$A$11:$A$86,0)),0))</f>
-        <v>46460</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F63,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G63,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H63,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I63,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J63,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K63,$A$11:$A$94,0)),0))</f>
+        <v>46422</v>
       </c>
       <c r="M63" s="18">
         <f>IF(E63=0,IF(COUNTA(F63:K63)=0,$D$2,L63),WORKDAY.INTL(L63,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46461</v>
+        <v>46425</v>
       </c>
       <c r="N63" s="18">
         <f>IF(E63=0,M63,WORKDAY.INTL(M63,E63-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46475</v>
-      </c>
-      <c r="O63" s="19"/>
+        <v>46447</v>
+      </c>
+      <c r="O63" s="19" t="s">
+        <v>68</v>
+      </c>
       <c r="P63" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:87">
+    <row r="64" spans="1:87" ht="26" customHeight="1">
       <c r="A64" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="D64" s="17">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E64" s="15">
-        <f>IF(D64=0,0,MAX(1,ROUNDUP(D64/$D$5,0)))</f>
-        <v>12</v>
+        <f>D64</f>
+        <v>5</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="G64" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="H64" s="15" t="s">
-        <v>88</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
       <c r="K64" s="15"/>
       <c r="L64" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J64,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K64,$A$11:$A$86,0)),0))</f>
-        <v>46460</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F64,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G64,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H64,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I64,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J64,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K64,$A$11:$A$94,0)),0))</f>
+        <v>46447</v>
       </c>
       <c r="M64" s="18">
         <f>IF(E64=0,IF(COUNTA(F64:K64)=0,$D$2,L64),WORKDAY.INTL(L64,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46461</v>
+        <v>46448</v>
       </c>
       <c r="N64" s="18">
         <f>IF(E64=0,M64,WORKDAY.INTL(M64,E64-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46476</v>
-      </c>
-      <c r="O64" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46454</v>
+      </c>
+      <c r="O64" s="19"/>
       <c r="P64" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:87">
@@ -5033,80 +5036,78 @@
         <v>205</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="D65" s="17">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E65" s="15">
-        <f>IF(D65=0,0,MAX(1,ROUNDUP(D65/$D$5,0)))</f>
-        <v>7</v>
+        <f>D65</f>
+        <v>40</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="G65" s="15" t="s">
-        <v>88</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="G65" s="15"/>
       <c r="H65" s="15"/>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
       <c r="K65" s="15"/>
       <c r="L65" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J65,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K65,$A$11:$A$86,0)),0))</f>
-        <v>46435</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F65,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G65,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H65,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I65,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J65,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K65,$A$11:$A$94,0)),0))</f>
+        <v>46454</v>
       </c>
       <c r="M65" s="18">
         <f>IF(E65=0,IF(COUNTA(F65:K65)=0,$D$2,L65),WORKDAY.INTL(L65,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46436</v>
+        <v>46455</v>
       </c>
       <c r="N65" s="18">
         <f>IF(E65=0,M65,WORKDAY.INTL(M65,E65-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46446</v>
+        <v>46517</v>
       </c>
       <c r="O65" s="19"/>
       <c r="P65" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:87">
       <c r="A66" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B66" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="C66" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="C66" s="16" t="s">
-        <v>209</v>
-      </c>
       <c r="D66" s="17">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E66" s="15">
         <f>IF(D66=0,0,MAX(1,ROUNDUP(D66/$D$5,0)))</f>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="G66" s="15" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
       <c r="K66" s="15"/>
       <c r="L66" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J66,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K66,$A$11:$A$86,0)),0))</f>
-        <v>46434</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F66,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G66,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H66,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I66,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J66,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K66,$A$11:$A$94,0)),0))</f>
+        <v>46454</v>
       </c>
       <c r="M66" s="18">
         <f>IF(E66=0,IF(COUNTA(F66:K66)=0,$D$2,L66),WORKDAY.INTL(L66,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46435</v>
+        <v>46455</v>
       </c>
       <c r="N66" s="18">
         <f>IF(E66=0,M66,WORKDAY.INTL(M66,E66-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46454</v>
+        <v>46462</v>
       </c>
       <c r="O66" s="19"/>
       <c r="P66" s="15" t="s">
@@ -5115,46 +5116,42 @@
     </row>
     <row r="67" spans="1:87">
       <c r="A67" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B67" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="C67" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C67" s="16" t="s">
-        <v>212</v>
-      </c>
       <c r="D67" s="17">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E67" s="15">
         <f>IF(D67=0,0,MAX(1,ROUNDUP(D67/$D$5,0)))</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="I67" s="15" t="s">
-        <v>88</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
       <c r="L67" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J67,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K67,$A$11:$A$86,0)),0))</f>
-        <v>46476</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F67,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G67,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H67,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I67,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J67,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K67,$A$11:$A$94,0)),0))</f>
+        <v>46517</v>
       </c>
       <c r="M67" s="18">
         <f>IF(E67=0,IF(COUNTA(F67:K67)=0,$D$2,L67),WORKDAY.INTL(L67,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46477</v>
+        <v>46518</v>
       </c>
       <c r="N67" s="18">
         <f>IF(E67=0,M67,WORKDAY.INTL(M67,E67-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46485</v>
+        <v>46523</v>
       </c>
       <c r="O67" s="19"/>
       <c r="P67" s="15" t="s">
@@ -5163,163 +5160,209 @@
     </row>
     <row r="68" spans="1:87">
       <c r="A68" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>214</v>
-      </c>
       <c r="C68" s="16" t="s">
-        <v>215</v>
+        <v>124</v>
       </c>
       <c r="D68" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E68" s="15">
         <f>IF(D68=0,0,MAX(1,ROUNDUP(D68/$D$5,0)))</f>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="I68" s="15"/>
+        <v>209</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>204</v>
+      </c>
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
       <c r="L68" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J68,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K68,$A$11:$A$86,0)),0))</f>
-        <v>46476</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F68,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G68,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H68,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I68,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J68,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K68,$A$11:$A$94,0)),0))</f>
+        <v>46523</v>
       </c>
       <c r="M68" s="18">
         <f>IF(E68=0,IF(COUNTA(F68:K68)=0,$D$2,L68),WORKDAY.INTL(L68,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46477</v>
+        <v>46524</v>
       </c>
       <c r="N68" s="18">
         <f>IF(E68=0,M68,WORKDAY.INTL(M68,E68-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46491</v>
-      </c>
-      <c r="O68" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46527</v>
+      </c>
+      <c r="O68" s="19"/>
       <c r="P68" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:87">
-      <c r="A69" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B69" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="D69" s="17">
-        <v>15</v>
-      </c>
-      <c r="E69" s="15">
-        <f>IF(D69=0,0,MAX(1,ROUNDUP(D69/$D$5,0)))</f>
-        <v>13</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="G69" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="H69" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="I69" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J69,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K69,$A$11:$A$86,0)),0))</f>
-        <v>46491</v>
-      </c>
-      <c r="M69" s="18">
-        <f>IF(E69=0,IF(COUNTA(F69:K69)=0,$D$2,L69),WORKDAY.INTL(L69,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46492</v>
-      </c>
-      <c r="N69" s="18">
-        <f>IF(E69=0,M69,WORKDAY.INTL(M69,E69-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46517</v>
-      </c>
-      <c r="O69" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="P69" s="15" t="s">
-        <v>69</v>
-      </c>
+      <c r="A69" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13"/>
+      <c r="P69" s="13"/>
+      <c r="R69" s="14"/>
+      <c r="S69" s="14"/>
+      <c r="T69" s="14"/>
+      <c r="U69" s="14"/>
+      <c r="V69" s="14"/>
+      <c r="W69" s="14"/>
+      <c r="X69" s="14"/>
+      <c r="Y69" s="14"/>
+      <c r="Z69" s="14"/>
+      <c r="AA69" s="14"/>
+      <c r="AB69" s="14"/>
+      <c r="AC69" s="14"/>
+      <c r="AD69" s="14"/>
+      <c r="AE69" s="14"/>
+      <c r="AF69" s="14"/>
+      <c r="AG69" s="14"/>
+      <c r="AH69" s="14"/>
+      <c r="AI69" s="14"/>
+      <c r="AJ69" s="14"/>
+      <c r="AK69" s="14"/>
+      <c r="AL69" s="14"/>
+      <c r="AM69" s="14"/>
+      <c r="AN69" s="14"/>
+      <c r="AO69" s="14"/>
+      <c r="AP69" s="14"/>
+      <c r="AQ69" s="14"/>
+      <c r="AR69" s="14"/>
+      <c r="AS69" s="14"/>
+      <c r="AT69" s="14"/>
+      <c r="AU69" s="14"/>
+      <c r="AV69" s="14"/>
+      <c r="AW69" s="14"/>
+      <c r="AX69" s="14"/>
+      <c r="AY69" s="14"/>
+      <c r="AZ69" s="14"/>
+      <c r="BA69" s="14"/>
+      <c r="BB69" s="14"/>
+      <c r="BC69" s="14"/>
+      <c r="BD69" s="14"/>
+      <c r="BE69" s="14"/>
+      <c r="BF69" s="14"/>
+      <c r="BG69" s="14"/>
+      <c r="BH69" s="14"/>
+      <c r="BI69" s="14"/>
+      <c r="BJ69" s="14"/>
+      <c r="BK69" s="14"/>
+      <c r="BL69" s="14"/>
+      <c r="BM69" s="14"/>
+      <c r="BN69" s="14"/>
+      <c r="BO69" s="14"/>
+      <c r="BP69" s="14"/>
+      <c r="BQ69" s="14"/>
+      <c r="BR69" s="14"/>
+      <c r="BS69" s="14"/>
+      <c r="BT69" s="14"/>
+      <c r="BU69" s="14"/>
+      <c r="BV69" s="14"/>
+      <c r="BW69" s="14"/>
+      <c r="BX69" s="14"/>
+      <c r="BY69" s="14"/>
+      <c r="BZ69" s="14"/>
+      <c r="CA69" s="14"/>
+      <c r="CB69" s="14"/>
+      <c r="CC69" s="14"/>
+      <c r="CD69" s="14"/>
+      <c r="CE69" s="14"/>
+      <c r="CF69" s="14"/>
+      <c r="CG69" s="14"/>
+      <c r="CH69" s="14"/>
+      <c r="CI69" s="14"/>
     </row>
     <row r="70" spans="1:87">
       <c r="A70" s="15" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D70" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E70" s="15">
         <f>IF(D70=0,0,MAX(1,ROUNDUP(D70/$D$5,0)))</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
+        <v>184</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="I70" s="15" t="s">
+        <v>220</v>
+      </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
       <c r="L70" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J70,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K70,$A$11:$A$86,0)),0))</f>
-        <v>46517</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F70,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G70,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H70,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I70,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J70,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K70,$A$11:$A$94,0)),0))</f>
+        <v>46476</v>
       </c>
       <c r="M70" s="18">
         <f>IF(E70=0,IF(COUNTA(F70:K70)=0,$D$2,L70),WORKDAY.INTL(L70,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46518</v>
+        <v>46477</v>
       </c>
       <c r="N70" s="18">
         <f>IF(E70=0,M70,WORKDAY.INTL(M70,E70-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46527</v>
+        <v>46491</v>
       </c>
       <c r="O70" s="19"/>
       <c r="P70" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:87">
+    <row r="71" spans="1:87" ht="26" customHeight="1">
       <c r="A71" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="D71" s="17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E71" s="15">
-        <f>IF(D71=0,0,MAX(1,ROUNDUP(D71/$D$5,0)))</f>
-        <v>3</v>
+        <f>D71</f>
+        <v>8</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="G71" s="15"/>
       <c r="H71" s="15"/>
@@ -5327,198 +5370,150 @@
       <c r="J71" s="15"/>
       <c r="K71" s="15"/>
       <c r="L71" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J71,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K71,$A$11:$A$86,0)),0))</f>
-        <v>46517</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F71,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G71,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H71,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I71,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J71,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K71,$A$11:$A$94,0)),0))</f>
+        <v>46460</v>
       </c>
       <c r="M71" s="18">
         <f>IF(E71=0,IF(COUNTA(F71:K71)=0,$D$2,L71),WORKDAY.INTL(L71,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46518</v>
+        <v>46461</v>
       </c>
       <c r="N71" s="18">
         <f>IF(E71=0,M71,WORKDAY.INTL(M71,E71-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46523</v>
+        <v>46470</v>
       </c>
       <c r="O71" s="19"/>
       <c r="P71" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:87">
       <c r="A72" s="15" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D72" s="17">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E72" s="15">
         <f>IF(D72=0,0,MAX(1,ROUNDUP(D72/$D$5,0)))</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="I72" s="15"/>
       <c r="J72" s="15"/>
       <c r="K72" s="15"/>
       <c r="L72" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J72,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K72,$A$11:$A$86,0)),0))</f>
-        <v>46517</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F72,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G72,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H72,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I72,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J72,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K72,$A$11:$A$94,0)),0))</f>
+        <v>46460</v>
       </c>
       <c r="M72" s="18">
         <f>IF(E72=0,IF(COUNTA(F72:K72)=0,$D$2,L72),WORKDAY.INTL(L72,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46518</v>
+        <v>46461</v>
       </c>
       <c r="N72" s="18">
         <f>IF(E72=0,M72,WORKDAY.INTL(M72,E72-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46527</v>
-      </c>
-      <c r="O72" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46476</v>
+      </c>
+      <c r="O72" s="19"/>
       <c r="P72" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:87">
-      <c r="A73" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
-      <c r="P73" s="13"/>
-      <c r="R73" s="14"/>
-      <c r="S73" s="14"/>
-      <c r="T73" s="14"/>
-      <c r="U73" s="14"/>
-      <c r="V73" s="14"/>
-      <c r="W73" s="14"/>
-      <c r="X73" s="14"/>
-      <c r="Y73" s="14"/>
-      <c r="Z73" s="14"/>
-      <c r="AA73" s="14"/>
-      <c r="AB73" s="14"/>
-      <c r="AC73" s="14"/>
-      <c r="AD73" s="14"/>
-      <c r="AE73" s="14"/>
-      <c r="AF73" s="14"/>
-      <c r="AG73" s="14"/>
-      <c r="AH73" s="14"/>
-      <c r="AI73" s="14"/>
-      <c r="AJ73" s="14"/>
-      <c r="AK73" s="14"/>
-      <c r="AL73" s="14"/>
-      <c r="AM73" s="14"/>
-      <c r="AN73" s="14"/>
-      <c r="AO73" s="14"/>
-      <c r="AP73" s="14"/>
-      <c r="AQ73" s="14"/>
-      <c r="AR73" s="14"/>
-      <c r="AS73" s="14"/>
-      <c r="AT73" s="14"/>
-      <c r="AU73" s="14"/>
-      <c r="AV73" s="14"/>
-      <c r="AW73" s="14"/>
-      <c r="AX73" s="14"/>
-      <c r="AY73" s="14"/>
-      <c r="AZ73" s="14"/>
-      <c r="BA73" s="14"/>
-      <c r="BB73" s="14"/>
-      <c r="BC73" s="14"/>
-      <c r="BD73" s="14"/>
-      <c r="BE73" s="14"/>
-      <c r="BF73" s="14"/>
-      <c r="BG73" s="14"/>
-      <c r="BH73" s="14"/>
-      <c r="BI73" s="14"/>
-      <c r="BJ73" s="14"/>
-      <c r="BK73" s="14"/>
-      <c r="BL73" s="14"/>
-      <c r="BM73" s="14"/>
-      <c r="BN73" s="14"/>
-      <c r="BO73" s="14"/>
-      <c r="BP73" s="14"/>
-      <c r="BQ73" s="14"/>
-      <c r="BR73" s="14"/>
-      <c r="BS73" s="14"/>
-      <c r="BT73" s="14"/>
-      <c r="BU73" s="14"/>
-      <c r="BV73" s="14"/>
-      <c r="BW73" s="14"/>
-      <c r="BX73" s="14"/>
-      <c r="BY73" s="14"/>
-      <c r="BZ73" s="14"/>
-      <c r="CA73" s="14"/>
-      <c r="CB73" s="14"/>
-      <c r="CC73" s="14"/>
-      <c r="CD73" s="14"/>
-      <c r="CE73" s="14"/>
-      <c r="CF73" s="14"/>
-      <c r="CG73" s="14"/>
-      <c r="CH73" s="14"/>
-      <c r="CI73" s="14"/>
+      <c r="A73" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D73" s="17">
+        <v>8</v>
+      </c>
+      <c r="E73" s="15">
+        <f>IF(D73=0,0,MAX(1,ROUNDUP(D73/$D$5,0)))</f>
+        <v>7</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="G73" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F73,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G73,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H73,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I73,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J73,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K73,$A$11:$A$94,0)),0))</f>
+        <v>46435</v>
+      </c>
+      <c r="M73" s="18">
+        <f>IF(E73=0,IF(COUNTA(F73:K73)=0,$D$2,L73),WORKDAY.INTL(L73,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46436</v>
+      </c>
+      <c r="N73" s="18">
+        <f>IF(E73=0,M73,WORKDAY.INTL(M73,E73-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46446</v>
+      </c>
+      <c r="O73" s="19"/>
+      <c r="P73" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="74" spans="1:87">
       <c r="A74" s="15" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="D74" s="17">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E74" s="15">
         <f>IF(D74=0,0,MAX(1,ROUNDUP(D74/$D$5,0)))</f>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H74" s="15"/>
       <c r="I74" s="15"/>
       <c r="J74" s="15"/>
       <c r="K74" s="15"/>
       <c r="L74" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J74,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K74,$A$11:$A$86,0)),0))</f>
-        <v>46390</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F74,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G74,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H74,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I74,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J74,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K74,$A$11:$A$94,0)),0))</f>
+        <v>46434</v>
       </c>
       <c r="M74" s="18">
         <f>IF(E74=0,IF(COUNTA(F74:K74)=0,$D$2,L74),WORKDAY.INTL(L74,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46391</v>
+        <v>46435</v>
       </c>
       <c r="N74" s="18">
         <f>IF(E74=0,M74,WORKDAY.INTL(M74,E74-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46397</v>
+        <v>46454</v>
       </c>
       <c r="O74" s="19"/>
       <c r="P74" s="15" t="s">
@@ -5527,40 +5522,46 @@
     </row>
     <row r="75" spans="1:87">
       <c r="A75" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C75" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="B75" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>233</v>
-      </c>
       <c r="D75" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E75" s="15">
         <f>IF(D75=0,0,MAX(1,ROUNDUP(D75/$D$5,0)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
-      <c r="I75" s="15"/>
+        <v>218</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="I75" s="15" t="s">
+        <v>94</v>
+      </c>
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
       <c r="L75" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J75,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K75,$A$11:$A$86,0)),0))</f>
-        <v>46468</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F75,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G75,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H75,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I75,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J75,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K75,$A$11:$A$94,0)),0))</f>
+        <v>46476</v>
       </c>
       <c r="M75" s="18">
         <f>IF(E75=0,IF(COUNTA(F75:K75)=0,$D$2,L75),WORKDAY.INTL(L75,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46469</v>
+        <v>46477</v>
       </c>
       <c r="N75" s="18">
         <f>IF(E75=0,M75,WORKDAY.INTL(M75,E75-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46478</v>
+        <v>46485</v>
       </c>
       <c r="O75" s="19"/>
       <c r="P75" s="15" t="s">
@@ -5569,40 +5570,44 @@
     </row>
     <row r="76" spans="1:87">
       <c r="A76" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="B76" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>236</v>
-      </c>
       <c r="D76" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E76" s="15">
         <f>IF(D76=0,0,MAX(1,ROUNDUP(D76/$D$5,0)))</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
+        <v>215</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="I76" s="15"/>
       <c r="J76" s="15"/>
       <c r="K76" s="15"/>
       <c r="L76" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J76,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K76,$A$11:$A$86,0)),0))</f>
-        <v>46478</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F76,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G76,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H76,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I76,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J76,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K76,$A$11:$A$94,0)),0))</f>
+        <v>46491</v>
       </c>
       <c r="M76" s="18">
         <f>IF(E76=0,IF(COUNTA(F76:K76)=0,$D$2,L76),WORKDAY.INTL(L76,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46481</v>
+        <v>46492</v>
       </c>
       <c r="N76" s="18">
         <f>IF(E76=0,M76,WORKDAY.INTL(M76,E76-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46488</v>
+        <v>46513</v>
       </c>
       <c r="O76" s="19"/>
       <c r="P76" s="15" t="s">
@@ -5611,137 +5616,97 @@
     </row>
     <row r="77" spans="1:87">
       <c r="A77" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C77" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>239</v>
-      </c>
       <c r="D77" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E77" s="15">
         <f>IF(D77=0,0,MAX(1,ROUNDUP(D77/$D$5,0)))</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G77" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
+        <v>219</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="I77" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="J77" s="15" t="s">
+        <v>204</v>
+      </c>
       <c r="K77" s="15"/>
       <c r="L77" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J77,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K77,$A$11:$A$86,0)),0))</f>
-        <v>46488</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F77,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G77,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H77,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I77,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J77,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K77,$A$11:$A$94,0)),0))</f>
+        <v>46517</v>
       </c>
       <c r="M77" s="18">
         <f>IF(E77=0,IF(COUNTA(F77:K77)=0,$D$2,L77),WORKDAY.INTL(L77,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46489</v>
+        <v>46518</v>
       </c>
       <c r="N77" s="18">
         <f>IF(E77=0,M77,WORKDAY.INTL(M77,E77-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46509</v>
-      </c>
-      <c r="O77" s="19"/>
+        <v>46537</v>
+      </c>
+      <c r="O77" s="19" t="s">
+        <v>68</v>
+      </c>
       <c r="P77" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:87">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C78" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
-      <c r="K78" s="13"/>
-      <c r="L78" s="13"/>
-      <c r="M78" s="13"/>
-      <c r="N78" s="13"/>
-      <c r="O78" s="13"/>
-      <c r="P78" s="13"/>
-      <c r="R78" s="14"/>
-      <c r="S78" s="14"/>
-      <c r="T78" s="14"/>
-      <c r="U78" s="14"/>
-      <c r="V78" s="14"/>
-      <c r="W78" s="14"/>
-      <c r="X78" s="14"/>
-      <c r="Y78" s="14"/>
-      <c r="Z78" s="14"/>
-      <c r="AA78" s="14"/>
-      <c r="AB78" s="14"/>
-      <c r="AC78" s="14"/>
-      <c r="AD78" s="14"/>
-      <c r="AE78" s="14"/>
-      <c r="AF78" s="14"/>
-      <c r="AG78" s="14"/>
-      <c r="AH78" s="14"/>
-      <c r="AI78" s="14"/>
-      <c r="AJ78" s="14"/>
-      <c r="AK78" s="14"/>
-      <c r="AL78" s="14"/>
-      <c r="AM78" s="14"/>
-      <c r="AN78" s="14"/>
-      <c r="AO78" s="14"/>
-      <c r="AP78" s="14"/>
-      <c r="AQ78" s="14"/>
-      <c r="AR78" s="14"/>
-      <c r="AS78" s="14"/>
-      <c r="AT78" s="14"/>
-      <c r="AU78" s="14"/>
-      <c r="AV78" s="14"/>
-      <c r="AW78" s="14"/>
-      <c r="AX78" s="14"/>
-      <c r="AY78" s="14"/>
-      <c r="AZ78" s="14"/>
-      <c r="BA78" s="14"/>
-      <c r="BB78" s="14"/>
-      <c r="BC78" s="14"/>
-      <c r="BD78" s="14"/>
-      <c r="BE78" s="14"/>
-      <c r="BF78" s="14"/>
-      <c r="BG78" s="14"/>
-      <c r="BH78" s="14"/>
-      <c r="BI78" s="14"/>
-      <c r="BJ78" s="14"/>
-      <c r="BK78" s="14"/>
-      <c r="BL78" s="14"/>
-      <c r="BM78" s="14"/>
-      <c r="BN78" s="14"/>
-      <c r="BO78" s="14"/>
-      <c r="BP78" s="14"/>
-      <c r="BQ78" s="14"/>
-      <c r="BR78" s="14"/>
-      <c r="BS78" s="14"/>
-      <c r="BT78" s="14"/>
-      <c r="BU78" s="14"/>
-      <c r="BV78" s="14"/>
-      <c r="BW78" s="14"/>
-      <c r="BX78" s="14"/>
-      <c r="BY78" s="14"/>
-      <c r="BZ78" s="14"/>
-      <c r="CA78" s="14"/>
-      <c r="CB78" s="14"/>
-      <c r="CC78" s="14"/>
-      <c r="CD78" s="14"/>
-      <c r="CE78" s="14"/>
-      <c r="CF78" s="14"/>
-      <c r="CG78" s="14"/>
-      <c r="CH78" s="14"/>
-      <c r="CI78" s="14"/>
+      <c r="D78" s="17">
+        <v>8</v>
+      </c>
+      <c r="E78" s="15">
+        <f>IF(D78=0,0,MAX(1,ROUNDUP(D78/$D$5,0)))</f>
+        <v>7</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="G78" s="15"/>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
+      <c r="L78" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F78,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G78,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H78,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I78,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J78,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K78,$A$11:$A$94,0)),0))</f>
+        <v>46537</v>
+      </c>
+      <c r="M78" s="18">
+        <f>IF(E78=0,IF(COUNTA(F78:K78)=0,$D$2,L78),WORKDAY.INTL(L78,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46538</v>
+      </c>
+      <c r="N78" s="18">
+        <f>IF(E78=0,M78,WORKDAY.INTL(M78,E78-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46546</v>
+      </c>
+      <c r="O78" s="19"/>
+      <c r="P78" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="79" spans="1:87">
       <c r="A79" s="15" t="s">
@@ -5751,7 +5716,7 @@
         <v>242</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="D79" s="17">
         <v>3</v>
@@ -5761,30 +5726,24 @@
         <v>3</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="G79" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="H79" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="I79" s="15" t="s">
-        <v>229</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="G79" s="15"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
       <c r="J79" s="15"/>
       <c r="K79" s="15"/>
       <c r="L79" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J79,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K79,$A$11:$A$86,0)),0))</f>
-        <v>46527</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F79,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G79,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H79,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I79,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J79,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K79,$A$11:$A$94,0)),0))</f>
+        <v>46537</v>
       </c>
       <c r="M79" s="18">
         <f>IF(E79=0,IF(COUNTA(F79:K79)=0,$D$2,L79),WORKDAY.INTL(L79,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46530</v>
+        <v>46538</v>
       </c>
       <c r="N79" s="18">
         <f>IF(E79=0,M79,WORKDAY.INTL(M79,E79-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46532</v>
+        <v>46540</v>
       </c>
       <c r="O79" s="19"/>
       <c r="P79" s="15" t="s">
@@ -5793,40 +5752,44 @@
     </row>
     <row r="80" spans="1:87">
       <c r="A80" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>67</v>
+        <v>246</v>
       </c>
       <c r="D80" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E80" s="15">
         <f>IF(D80=0,0,MAX(1,ROUNDUP(D80/$D$5,0)))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
+        <v>235</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="I80" s="15"/>
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
       <c r="L80" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J80,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K80,$A$11:$A$86,0)),0))</f>
-        <v>46527</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F80,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G80,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H80,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I80,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J80,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K80,$A$11:$A$94,0)),0))</f>
+        <v>46537</v>
       </c>
       <c r="M80" s="18">
         <f>IF(E80=0,IF(COUNTA(F80:K80)=0,$D$2,L80),WORKDAY.INTL(L80,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46530</v>
+        <v>46538</v>
       </c>
       <c r="N80" s="18">
         <f>IF(E80=0,M80,WORKDAY.INTL(M80,E80-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46533</v>
+        <v>46546</v>
       </c>
       <c r="O80" s="19" t="s">
         <v>68</v>
@@ -5835,165 +5798,203 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
-      <c r="A81" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="C81" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D81" s="17">
-        <v>3</v>
-      </c>
-      <c r="E81" s="15">
-        <f>IF(D81=0,0,MAX(1,ROUNDUP(D81/$D$5,0)))</f>
-        <v>3</v>
-      </c>
-      <c r="F81" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="G81" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="H81" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="I81" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="J81" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="K81" s="15"/>
-      <c r="L81" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J81,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K81,$A$11:$A$86,0)),0))</f>
-        <v>46527</v>
-      </c>
-      <c r="M81" s="18">
-        <f>IF(E81=0,IF(COUNTA(F81:K81)=0,$D$2,L81),WORKDAY.INTL(L81,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46530</v>
-      </c>
-      <c r="N81" s="18">
-        <f>IF(E81=0,M81,WORKDAY.INTL(M81,E81-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46532</v>
-      </c>
-      <c r="O81" s="19"/>
-      <c r="P81" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16">
+    <row r="81" spans="1:87">
+      <c r="A81" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B81" s="13"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
+      <c r="K81" s="13"/>
+      <c r="L81" s="13"/>
+      <c r="M81" s="13"/>
+      <c r="N81" s="13"/>
+      <c r="O81" s="13"/>
+      <c r="P81" s="13"/>
+      <c r="R81" s="14"/>
+      <c r="S81" s="14"/>
+      <c r="T81" s="14"/>
+      <c r="U81" s="14"/>
+      <c r="V81" s="14"/>
+      <c r="W81" s="14"/>
+      <c r="X81" s="14"/>
+      <c r="Y81" s="14"/>
+      <c r="Z81" s="14"/>
+      <c r="AA81" s="14"/>
+      <c r="AB81" s="14"/>
+      <c r="AC81" s="14"/>
+      <c r="AD81" s="14"/>
+      <c r="AE81" s="14"/>
+      <c r="AF81" s="14"/>
+      <c r="AG81" s="14"/>
+      <c r="AH81" s="14"/>
+      <c r="AI81" s="14"/>
+      <c r="AJ81" s="14"/>
+      <c r="AK81" s="14"/>
+      <c r="AL81" s="14"/>
+      <c r="AM81" s="14"/>
+      <c r="AN81" s="14"/>
+      <c r="AO81" s="14"/>
+      <c r="AP81" s="14"/>
+      <c r="AQ81" s="14"/>
+      <c r="AR81" s="14"/>
+      <c r="AS81" s="14"/>
+      <c r="AT81" s="14"/>
+      <c r="AU81" s="14"/>
+      <c r="AV81" s="14"/>
+      <c r="AW81" s="14"/>
+      <c r="AX81" s="14"/>
+      <c r="AY81" s="14"/>
+      <c r="AZ81" s="14"/>
+      <c r="BA81" s="14"/>
+      <c r="BB81" s="14"/>
+      <c r="BC81" s="14"/>
+      <c r="BD81" s="14"/>
+      <c r="BE81" s="14"/>
+      <c r="BF81" s="14"/>
+      <c r="BG81" s="14"/>
+      <c r="BH81" s="14"/>
+      <c r="BI81" s="14"/>
+      <c r="BJ81" s="14"/>
+      <c r="BK81" s="14"/>
+      <c r="BL81" s="14"/>
+      <c r="BM81" s="14"/>
+      <c r="BN81" s="14"/>
+      <c r="BO81" s="14"/>
+      <c r="BP81" s="14"/>
+      <c r="BQ81" s="14"/>
+      <c r="BR81" s="14"/>
+      <c r="BS81" s="14"/>
+      <c r="BT81" s="14"/>
+      <c r="BU81" s="14"/>
+      <c r="BV81" s="14"/>
+      <c r="BW81" s="14"/>
+      <c r="BX81" s="14"/>
+      <c r="BY81" s="14"/>
+      <c r="BZ81" s="14"/>
+      <c r="CA81" s="14"/>
+      <c r="CB81" s="14"/>
+      <c r="CC81" s="14"/>
+      <c r="CD81" s="14"/>
+      <c r="CE81" s="14"/>
+      <c r="CF81" s="14"/>
+      <c r="CG81" s="14"/>
+      <c r="CH81" s="14"/>
+      <c r="CI81" s="14"/>
+    </row>
+    <row r="82" spans="1:87">
       <c r="A82" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D82" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E82" s="15">
-        <f>D82</f>
-        <v>3</v>
+        <f>IF(D82=0,0,MAX(1,ROUNDUP(D82/$D$5,0)))</f>
+        <v>5</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>241</v>
+        <v>79</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="H82" s="15" t="s">
-        <v>245</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="H82" s="15"/>
       <c r="I82" s="15"/>
       <c r="J82" s="15"/>
       <c r="K82" s="15"/>
       <c r="L82" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J82,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K82,$A$11:$A$86,0)),0))</f>
-        <v>46533</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F82,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G82,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H82,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I82,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J82,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K82,$A$11:$A$94,0)),0))</f>
+        <v>46390</v>
       </c>
       <c r="M82" s="18">
         <f>IF(E82=0,IF(COUNTA(F82:K82)=0,$D$2,L82),WORKDAY.INTL(L82,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46534</v>
+        <v>46391</v>
       </c>
       <c r="N82" s="18">
         <f>IF(E82=0,M82,WORKDAY.INTL(M82,E82-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46538</v>
-      </c>
-      <c r="O82" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46397</v>
+      </c>
+      <c r="O82" s="19"/>
       <c r="P82" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:87">
       <c r="A83" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>67</v>
+        <v>252</v>
       </c>
       <c r="D83" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E83" s="15">
         <f>IF(D83=0,0,MAX(1,ROUNDUP(D83/$D$5,0)))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="G83" s="15"/>
+        <v>200</v>
+      </c>
+      <c r="G83" s="15" t="s">
+        <v>156</v>
+      </c>
       <c r="H83" s="15"/>
       <c r="I83" s="15"/>
       <c r="J83" s="15"/>
       <c r="K83" s="15"/>
       <c r="L83" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J83,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K83,$A$11:$A$86,0)),0))</f>
-        <v>46538</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F83,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G83,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H83,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I83,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J83,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K83,$A$11:$A$94,0)),0))</f>
+        <v>46447</v>
       </c>
       <c r="M83" s="18">
         <f>IF(E83=0,IF(COUNTA(F83:K83)=0,$D$2,L83),WORKDAY.INTL(L83,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46539</v>
+        <v>46448</v>
       </c>
       <c r="N83" s="18">
         <f>IF(E83=0,M83,WORKDAY.INTL(M83,E83-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46547</v>
+        <v>46457</v>
       </c>
       <c r="O83" s="19"/>
       <c r="P83" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="26" customHeight="1">
+    <row r="84" spans="1:87">
       <c r="A84" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>67</v>
+        <v>255</v>
       </c>
       <c r="D84" s="17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E84" s="15">
-        <f>D84</f>
-        <v>10</v>
+        <f>IF(D84=0,0,MAX(1,ROUNDUP(D84/$D$5,0)))</f>
+        <v>6</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G84" s="15"/>
       <c r="H84" s="15"/>
@@ -6001,179 +6002,589 @@
       <c r="J84" s="15"/>
       <c r="K84" s="15"/>
       <c r="L84" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J84,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K84,$A$11:$A$86,0)),0))</f>
-        <v>46538</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F84,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G84,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H84,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I84,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J84,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K84,$A$11:$A$94,0)),0))</f>
+        <v>46457</v>
       </c>
       <c r="M84" s="18">
         <f>IF(E84=0,IF(COUNTA(F84:K84)=0,$D$2,L84),WORKDAY.INTL(L84,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46539</v>
+        <v>46460</v>
       </c>
       <c r="N84" s="18">
         <f>IF(E84=0,M84,WORKDAY.INTL(M84,E84-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46552</v>
-      </c>
-      <c r="O84" s="19" t="s">
-        <v>68</v>
-      </c>
+        <v>46467</v>
+      </c>
+      <c r="O84" s="19"/>
       <c r="P84" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:87">
       <c r="A85" s="15" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>67</v>
+        <v>258</v>
       </c>
       <c r="D85" s="17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E85" s="15">
         <f>IF(D85=0,0,MAX(1,ROUNDUP(D85/$D$5,0)))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="G85" s="15"/>
+        <v>253</v>
+      </c>
+      <c r="G85" s="15" t="s">
+        <v>226</v>
+      </c>
       <c r="H85" s="15"/>
       <c r="I85" s="15"/>
       <c r="J85" s="15"/>
       <c r="K85" s="15"/>
       <c r="L85" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J85,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K85,$A$11:$A$86,0)),0))</f>
-        <v>46547</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F85,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G85,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H85,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I85,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J85,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K85,$A$11:$A$94,0)),0))</f>
+        <v>46467</v>
       </c>
       <c r="M85" s="18">
         <f>IF(E85=0,IF(COUNTA(F85:K85)=0,$D$2,L85),WORKDAY.INTL(L85,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46547</v>
+        <v>46468</v>
       </c>
       <c r="N85" s="18">
         <f>IF(E85=0,M85,WORKDAY.INTL(M85,E85-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46547</v>
+        <v>46481</v>
       </c>
       <c r="O85" s="19"/>
       <c r="P85" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
-      <c r="A86" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="B86" s="16" t="s">
+    <row r="86" spans="1:87">
+      <c r="A86" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="13"/>
+      <c r="L86" s="13"/>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="13"/>
+      <c r="P86" s="13"/>
+      <c r="R86" s="14"/>
+      <c r="S86" s="14"/>
+      <c r="T86" s="14"/>
+      <c r="U86" s="14"/>
+      <c r="V86" s="14"/>
+      <c r="W86" s="14"/>
+      <c r="X86" s="14"/>
+      <c r="Y86" s="14"/>
+      <c r="Z86" s="14"/>
+      <c r="AA86" s="14"/>
+      <c r="AB86" s="14"/>
+      <c r="AC86" s="14"/>
+      <c r="AD86" s="14"/>
+      <c r="AE86" s="14"/>
+      <c r="AF86" s="14"/>
+      <c r="AG86" s="14"/>
+      <c r="AH86" s="14"/>
+      <c r="AI86" s="14"/>
+      <c r="AJ86" s="14"/>
+      <c r="AK86" s="14"/>
+      <c r="AL86" s="14"/>
+      <c r="AM86" s="14"/>
+      <c r="AN86" s="14"/>
+      <c r="AO86" s="14"/>
+      <c r="AP86" s="14"/>
+      <c r="AQ86" s="14"/>
+      <c r="AR86" s="14"/>
+      <c r="AS86" s="14"/>
+      <c r="AT86" s="14"/>
+      <c r="AU86" s="14"/>
+      <c r="AV86" s="14"/>
+      <c r="AW86" s="14"/>
+      <c r="AX86" s="14"/>
+      <c r="AY86" s="14"/>
+      <c r="AZ86" s="14"/>
+      <c r="BA86" s="14"/>
+      <c r="BB86" s="14"/>
+      <c r="BC86" s="14"/>
+      <c r="BD86" s="14"/>
+      <c r="BE86" s="14"/>
+      <c r="BF86" s="14"/>
+      <c r="BG86" s="14"/>
+      <c r="BH86" s="14"/>
+      <c r="BI86" s="14"/>
+      <c r="BJ86" s="14"/>
+      <c r="BK86" s="14"/>
+      <c r="BL86" s="14"/>
+      <c r="BM86" s="14"/>
+      <c r="BN86" s="14"/>
+      <c r="BO86" s="14"/>
+      <c r="BP86" s="14"/>
+      <c r="BQ86" s="14"/>
+      <c r="BR86" s="14"/>
+      <c r="BS86" s="14"/>
+      <c r="BT86" s="14"/>
+      <c r="BU86" s="14"/>
+      <c r="BV86" s="14"/>
+      <c r="BW86" s="14"/>
+      <c r="BX86" s="14"/>
+      <c r="BY86" s="14"/>
+      <c r="BZ86" s="14"/>
+      <c r="CA86" s="14"/>
+      <c r="CB86" s="14"/>
+      <c r="CC86" s="14"/>
+      <c r="CD86" s="14"/>
+      <c r="CE86" s="14"/>
+      <c r="CF86" s="14"/>
+      <c r="CG86" s="14"/>
+      <c r="CH86" s="14"/>
+      <c r="CI86" s="14"/>
+    </row>
+    <row r="87" spans="1:87">
+      <c r="A87" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="D87" s="17">
+        <v>3</v>
+      </c>
+      <c r="E87" s="15">
+        <f>IF(D87=0,0,MAX(1,ROUNDUP(D87/$D$5,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="G87" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="I87" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15"/>
+      <c r="L87" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F87,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G87,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H87,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I87,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J87,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K87,$A$11:$A$94,0)),0))</f>
+        <v>46546</v>
+      </c>
+      <c r="M87" s="18">
+        <f>IF(E87=0,IF(COUNTA(F87:K87)=0,$D$2,L87),WORKDAY.INTL(L87,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46547</v>
+      </c>
+      <c r="N87" s="18">
+        <f>IF(E87=0,M87,WORKDAY.INTL(M87,E87-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46551</v>
+      </c>
+      <c r="O87" s="19"/>
+      <c r="P87" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:87">
+      <c r="A88" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D88" s="17">
+        <v>4</v>
+      </c>
+      <c r="E88" s="15">
+        <f>IF(D88=0,0,MAX(1,ROUNDUP(D88/$D$5,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="G88" s="15"/>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
+      <c r="L88" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F88,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G88,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H88,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I88,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J88,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K88,$A$11:$A$94,0)),0))</f>
+        <v>46546</v>
+      </c>
+      <c r="M88" s="18">
+        <f>IF(E88=0,IF(COUNTA(F88:K88)=0,$D$2,L88),WORKDAY.INTL(L88,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46547</v>
+      </c>
+      <c r="N88" s="18">
+        <f>IF(E88=0,M88,WORKDAY.INTL(M88,E88-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46552</v>
+      </c>
+      <c r="O88" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="P88" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:87">
+      <c r="A89" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B89" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D89" s="17">
+        <v>3</v>
+      </c>
+      <c r="E89" s="15">
+        <f>IF(D89=0,0,MAX(1,ROUNDUP(D89/$D$5,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="H89" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="I89" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="J89" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="K89" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="L89" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F89,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G89,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H89,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I89,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J89,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K89,$A$11:$A$94,0)),0))</f>
+        <v>46546</v>
+      </c>
+      <c r="M89" s="18">
+        <f>IF(E89=0,IF(COUNTA(F89:K89)=0,$D$2,L89),WORKDAY.INTL(L89,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46547</v>
+      </c>
+      <c r="N89" s="18">
+        <f>IF(E89=0,M89,WORKDAY.INTL(M89,E89-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46551</v>
+      </c>
+      <c r="O89" s="19"/>
+      <c r="P89" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="90" spans="1:87">
+      <c r="A90" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C90" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="D86" s="17">
+      <c r="D90" s="17">
+        <v>3</v>
+      </c>
+      <c r="E90" s="15">
+        <f>D90</f>
+        <v>3</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="H90" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
+      <c r="L90" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F90,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G90,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H90,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I90,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J90,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K90,$A$11:$A$94,0)),0))</f>
+        <v>46552</v>
+      </c>
+      <c r="M90" s="18">
+        <f>IF(E90=0,IF(COUNTA(F90:K90)=0,$D$2,L90),WORKDAY.INTL(L90,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46553</v>
+      </c>
+      <c r="N90" s="18">
+        <f>IF(E90=0,M90,WORKDAY.INTL(M90,E90-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46555</v>
+      </c>
+      <c r="O90" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="P90" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:87">
+      <c r="A91" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="B91" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D91" s="17">
+        <v>8</v>
+      </c>
+      <c r="E91" s="15">
+        <f>IF(D91=0,0,MAX(1,ROUNDUP(D91/$D$5,0)))</f>
+        <v>7</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
+      <c r="L91" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F91,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G91,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H91,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I91,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J91,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K91,$A$11:$A$94,0)),0))</f>
+        <v>46555</v>
+      </c>
+      <c r="M91" s="18">
+        <f>IF(E91=0,IF(COUNTA(F91:K91)=0,$D$2,L91),WORKDAY.INTL(L91,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46558</v>
+      </c>
+      <c r="N91" s="18">
+        <f>IF(E91=0,M91,WORKDAY.INTL(M91,E91-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46566</v>
+      </c>
+      <c r="O91" s="19"/>
+      <c r="P91" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:87" ht="26" customHeight="1">
+      <c r="A92" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D92" s="17">
+        <v>10</v>
+      </c>
+      <c r="E92" s="15">
+        <f>D92</f>
+        <v>10</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="G92" s="15"/>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
+      <c r="L92" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F92,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G92,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H92,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I92,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J92,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K92,$A$11:$A$94,0)),0))</f>
+        <v>46555</v>
+      </c>
+      <c r="M92" s="18">
+        <f>IF(E92=0,IF(COUNTA(F92:K92)=0,$D$2,L92),WORKDAY.INTL(L92,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46558</v>
+      </c>
+      <c r="N92" s="18">
+        <f>IF(E92=0,M92,WORKDAY.INTL(M92,E92-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46569</v>
+      </c>
+      <c r="O92" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="P92" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="93" spans="1:87">
+      <c r="A93" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B93" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D93" s="17">
+        <v>0</v>
+      </c>
+      <c r="E93" s="15">
+        <f>IF(D93=0,0,MAX(1,ROUNDUP(D93/$D$5,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="G93" s="15"/>
+      <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
+      <c r="L93" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F93,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G93,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H93,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I93,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J93,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K93,$A$11:$A$94,0)),0))</f>
+        <v>46566</v>
+      </c>
+      <c r="M93" s="18">
+        <f>IF(E93=0,IF(COUNTA(F93:K93)=0,$D$2,L93),WORKDAY.INTL(L93,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46566</v>
+      </c>
+      <c r="N93" s="18">
+        <f>IF(E93=0,M93,WORKDAY.INTL(M93,E93-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46566</v>
+      </c>
+      <c r="O93" s="19"/>
+      <c r="P93" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="94" spans="1:87">
+      <c r="A94" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D94" s="17">
         <v>30</v>
       </c>
-      <c r="E86" s="15">
-        <f>D86</f>
+      <c r="E94" s="15">
+        <f>D94</f>
         <v>30</v>
       </c>
-      <c r="F86" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="G86" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="H86" s="15"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="15"/>
-      <c r="K86" s="15"/>
-      <c r="L86" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$86,MATCH(F86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(G86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(H86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(I86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(J86,$A$11:$A$86,0)),0),IFERROR(INDEX($N$11:$N$86,MATCH(K86,$A$11:$A$86,0)),0))</f>
-        <v>46552</v>
-      </c>
-      <c r="M86" s="18">
-        <f>IF(E86=0,IF(COUNTA(F86:K86)=0,$D$2,L86),WORKDAY.INTL(L86,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46553</v>
-      </c>
-      <c r="N86" s="18">
-        <f>IF(E86=0,M86,WORKDAY.INTL(M86,E86-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
-        <v>46594</v>
-      </c>
-      <c r="O86" s="19"/>
-      <c r="P86" s="15" t="s">
+      <c r="F94" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="G94" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
+      <c r="L94" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$11:$N$94,MATCH(F94,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(G94,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(H94,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(I94,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(J94,$A$11:$A$94,0)),0),IFERROR(INDEX($N$11:$N$94,MATCH(K94,$A$11:$A$94,0)),0))</f>
+        <v>46569</v>
+      </c>
+      <c r="M94" s="18">
+        <f>IF(E94=0,IF(COUNTA(F94:K94)=0,$D$2,L94),WORKDAY.INTL(L94,1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46572</v>
+      </c>
+      <c r="N94" s="18">
+        <f>IF(E94=0,M94,WORKDAY.INTL(M94,E94-1,$D$3,'לוח שנה וחגים'!$F$5:$F$20))</f>
+        <v>46611</v>
+      </c>
+      <c r="O94" s="19"/>
+      <c r="P94" s="15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
-      <c r="B88" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="N88" s="20">
-        <f>N85</f>
-        <v>46547</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16">
-      <c r="B89" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="N89" s="20">
-        <f>N86</f>
-        <v>46594</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16">
-      <c r="B90" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="N90" s="21">
-        <f>ROUND((N88-$D$2+1)/7,1)</f>
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16">
-      <c r="B91" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="N91" s="21">
-        <f>NETWORKDAYS.INTL($D$2,N88,$D$3,'לוח שנה וחגים'!$F$5:$F$20)</f>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16">
-      <c r="B92" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22"/>
-      <c r="H92" s="22"/>
-      <c r="I92" s="22"/>
-      <c r="J92" s="22"/>
-      <c r="K92" s="22"/>
-      <c r="L92" s="22"/>
-      <c r="M92" s="22"/>
-      <c r="N92" s="22"/>
-    </row>
-    <row r="93" spans="1:16">
-      <c r="B93" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="C93" s="22"/>
-      <c r="D93" s="22"/>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="22"/>
-      <c r="H93" s="22"/>
-      <c r="I93" s="22"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="22"/>
-      <c r="L93" s="22"/>
-      <c r="M93" s="22"/>
-      <c r="N93" s="22"/>
+    <row r="96" spans="1:87">
+      <c r="B96" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="N96" s="20">
+        <f>N93</f>
+        <v>46566</v>
+      </c>
+    </row>
+    <row r="97" spans="2:14">
+      <c r="B97" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="N97" s="20">
+        <f>N94</f>
+        <v>46611</v>
+      </c>
+    </row>
+    <row r="98" spans="2:14">
+      <c r="B98" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="N98" s="21">
+        <f>ROUND((N96-$D$2+1)/7,1)</f>
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="99" spans="2:14">
+      <c r="B99" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="N99" s="21">
+        <f>NETWORKDAYS.INTL($D$2,N96,$D$3,'לוח שנה וחגים'!$F$5:$F$20)</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="100" spans="2:14">
+      <c r="B100" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C100" s="22"/>
+      <c r="D100" s="22"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="22"/>
+      <c r="H100" s="22"/>
+      <c r="I100" s="22"/>
+      <c r="J100" s="22"/>
+      <c r="K100" s="22"/>
+      <c r="L100" s="22"/>
+      <c r="M100" s="22"/>
+      <c r="N100" s="22"/>
+    </row>
+    <row r="101" spans="2:14">
+      <c r="B101" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="C101" s="22"/>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
+      <c r="H101" s="22"/>
+      <c r="I101" s="22"/>
+      <c r="J101" s="22"/>
+      <c r="K101" s="22"/>
+      <c r="L101" s="22"/>
+      <c r="M101" s="22"/>
+      <c r="N101" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -6183,24 +6594,24 @@
     <mergeCell ref="A7:P7"/>
     <mergeCell ref="A8:P8"/>
     <mergeCell ref="A11:P11"/>
-    <mergeCell ref="A20:P20"/>
-    <mergeCell ref="A24:P24"/>
-    <mergeCell ref="A36:P36"/>
-    <mergeCell ref="A43:P43"/>
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="A57:P57"/>
-    <mergeCell ref="A62:P62"/>
-    <mergeCell ref="A73:P73"/>
-    <mergeCell ref="A78:P78"/>
-    <mergeCell ref="B92:N92"/>
-    <mergeCell ref="B93:N93"/>
+    <mergeCell ref="A22:P22"/>
+    <mergeCell ref="A26:P26"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A46:P46"/>
+    <mergeCell ref="A53:P53"/>
+    <mergeCell ref="A61:P61"/>
+    <mergeCell ref="A69:P69"/>
+    <mergeCell ref="A81:P81"/>
+    <mergeCell ref="A86:P86"/>
+    <mergeCell ref="B100:N100"/>
+    <mergeCell ref="B101:N101"/>
   </mergeCells>
   <conditionalFormatting sqref="R10:CI10">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R11:CI86">
+  <conditionalFormatting sqref="R11:CI94">
     <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>AND($E11=0,$A11&lt;&gt;"",$M11&gt;=R$9,$M11&lt;=R$9+6)</formula>
     </cfRule>
@@ -6634,18 +7045,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="9" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="60" customHeight="1">
@@ -6653,10 +7064,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1">
@@ -6664,10 +7075,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1">
@@ -6675,10 +7086,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1">
@@ -6686,10 +7097,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1">
@@ -6697,10 +7108,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1">
@@ -6708,10 +7119,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1">
@@ -6719,10 +7130,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1">
@@ -6730,15 +7141,15 @@
         <v>8</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="22" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -6761,18 +7172,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="9" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1">
@@ -6780,10 +7191,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1">
@@ -6791,10 +7202,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1">
@@ -6802,10 +7213,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1">
@@ -6813,10 +7224,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1">
@@ -6824,10 +7235,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1">
@@ -6835,10 +7246,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1">
@@ -6846,10 +7257,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
